--- a/reports/devops-jobs-israel-2026-W44.xlsx
+++ b/reports/devops-jobs-israel-2026-W44.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="493">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="498">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-26T12:46:33</t>
+    <t xml:space="preserve">2026-10-27T11:59:45</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -417,21 +417,6 @@
     <t xml:space="preserve">https://orca.security/about/careers/6149333004?gh_jid=6149333004</t>
   </si>
   <si>
-    <t xml:space="preserve">Platform Engineer- Edge Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Saltsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Terraform, Docker, CI/CD, Helm, Security, Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://salt.security/job-board?gh_jid=5208152007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-07</t>
-  </si>
-  <si>
     <t xml:space="preserve">Aidoc</t>
   </si>
   <si>
@@ -450,13 +435,13 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-mentee-robotics-4481407411</t>
   </si>
   <si>
-    <t xml:space="preserve">Wiz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiz-4406742504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-08</t>
+    <t xml:space="preserve">Senior DevOps Platform Engineer- CTI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dream</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-platform-engineer-cti-at-dream-4465727084</t>
   </si>
   <si>
     <t xml:space="preserve">Priority Software</t>
@@ -525,6 +510,15 @@
     <t xml:space="preserve">2026-10-25</t>
   </si>
   <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-comblack-4483574435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-27</t>
+  </si>
+  <si>
     <t xml:space="preserve">Senior Principal DevOps Engineer (Cortex Cloud)</t>
   </si>
   <si>
@@ -561,15 +555,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-bigid-4482680687</t>
   </si>
   <si>
-    <t xml:space="preserve">Play Perfect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-play-perfect-4469727405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-24</t>
-  </si>
-  <si>
     <t xml:space="preserve">DevOps Engineer - Cloud Infra Team</t>
   </si>
   <si>
@@ -618,12 +603,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-ai-team-at-bridgewise-4482680803</t>
   </si>
   <si>
-    <t xml:space="preserve">Blockaid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-blockaid-4480236011</t>
-  </si>
-  <si>
     <t xml:space="preserve">Platform DevOps Engineer - Core Platform</t>
   </si>
   <si>
@@ -639,6 +618,12 @@
     <t xml:space="preserve">2026-10-22</t>
   </si>
   <si>
+    <t xml:space="preserve">Experienced DevOps Engineer (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/experienced-devops-engineer-cortex-at-palo-alto-networks-4462513797</t>
+  </si>
+  <si>
     <t xml:space="preserve">Speedata.io</t>
   </si>
   <si>
@@ -651,10 +636,22 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-speedata-io-4483379335</t>
   </si>
   <si>
-    <t xml:space="preserve">Experienced DevOps Engineer (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/experienced-devops-engineer-cortex-at-palo-alto-networks-4462513797</t>
+    <t xml:space="preserve">Cloud DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-engineer-at-comblack-4483582140</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zenity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-zenity-4478465745</t>
   </si>
   <si>
     <t xml:space="preserve">Senior DevOps / Site Reliability Engineer (SRE)</t>
@@ -666,351 +663,372 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-site-reliability-engineer-sre-at-lendbuzz-4480488912</t>
   </si>
   <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-abra-4480795007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4481079700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SR DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bitsight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-bitsight-4483570331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personetics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-personetics-4428829912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeValue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-codevalue-4483726365</t>
+  </si>
+  <si>
     <t xml:space="preserve">Elementor</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-elementor-4482868447</t>
   </si>
   <si>
-    <t xml:space="preserve">Cellebrite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-cellebrite-4479674975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-abra-4480795007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4481079700</t>
+    <t xml:space="preserve">Pontera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-pontera-4481315450</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Webiks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-reliability-engineer-at-webiks-4483579517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-devops-engineer-at-jeen-ai-4482082697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Software Engineer, DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aiven</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-software-engineer-devops-at-aiven-4426867332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Founding DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stealth-Mode Cybersecurity Startup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/founding-devops-at-stealth-mode-cybersecurity-startup-4482932513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medulla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-medulla-4483534511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevSecOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PayPlus - The Future of Payments &amp; Commerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devsecops-engineer-at-payplus-the-future-of-payments-commerce-4482999139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Tech Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-wix-4483537365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-engineer-at-lendbuzz-4477980904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
   </si>
   <si>
     <t xml:space="preserve">Paragon</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Personetics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-personetics-4428829912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pontera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-pontera-4481315450</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-devops-engineer-at-jeen-ai-4482082697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Software Engineer, DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aiven</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-software-engineer-devops-at-aiven-4426867332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Founding DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stealth-Mode Cybersecurity Startup</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/founding-devops-at-stealth-mode-cybersecurity-startup-4482932513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medulla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-medulla-4483534511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Application DevOps Engineer (1006977)</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-paragon-4456184154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. SRE AI Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Navan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-sre-ai-engineer-at-navan-4437742346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential Careers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-confidential-careers-4476662621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Integrator – SRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compie Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-integrator-%E2%80%93-sre-at-compie-technologies-4483368453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure Engineer - Core Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-core-systems-at-wix-4483368404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infra Engineer Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infra-engineer-team-lead-at-dialog-4481085538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software System Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-system-reliability-engineer-at-cisco-4483388333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Backend Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akamai Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-backend-infrastructure-engineer-at-akamai-technologies-4473769865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Software Engineer -Platform Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viz.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-software-engineer-platform-team-at-viz-ai-4437383686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Immunai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-immunai-4482405033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Platform Engineer (Infra Platform)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">monday.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-infra-platform-at-monday-com-4483388052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ScaleOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-scaleops-4483763089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior GPU Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zesty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-gpu-platform-engineer-at-zesty-4481405125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal DevOps Engineer - AI Platforms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-ai-platforms-at-palo-alto-networks-4471749164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Millennium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-millennium-4482698329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-alice-formerly-activefence-4472729462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Platform Engineer (Mid-level)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobgether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-mid-level-at-jobgether-4481691238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guesty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-platform-engineer-at-guesty-4473205757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal Data Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MediaForce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-data-platform-engineer-at-mediaforce-4481460917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Infrastructure &amp; Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moon Active</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-cloud-engineer-at-moon-active-4447031167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-engineer-at-cato-networks-4463471007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DoiT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-doit-4463987032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moveo Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-infrastructure-engineer-at-moveo-source-4480775799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-elbit-systems-israel-4474036853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OpenShift Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/openshift-infrastructure-engineer-at-comblack-4483564559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer (37823)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-37823-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4482463663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Administrator (1007969)</t>
   </si>
   <si>
     <t xml:space="preserve">Elad Software Systems</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/application-devops-engineer-1006977-at-elad-software-systems-4481553636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Tech Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-wix-4483537365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-engineer-at-lendbuzz-4477980904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Millennium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-millennium-4482698329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevSecOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Antidote Health</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-antidote-health-4480773737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-paragon-4456184154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. SRE AI Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-sre-ai-engineer-at-navan-4437742346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential Careers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-confidential-careers-4476662621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Integrator – SRE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compie Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-integrator-%E2%80%93-sre-at-compie-technologies-4483368453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Integrator SRE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moveo Source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-integrator-sre-at-moveo-source-4481380188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure Engineer - Core Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-core-systems-at-wix-4483368404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infra Engineer Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dialog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infra-engineer-team-lead-at-dialog-4481085538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software System Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-system-reliability-engineer-at-cisco-4483388333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Backend Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akamai Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-backend-infrastructure-engineer-at-akamai-technologies-4473769865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Software Engineer -Platform Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viz.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-software-engineer-platform-team-at-viz-ai-4437383686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Immunai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-immunai-4482405033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Platform Engineer (Infra Platform)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monday.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-infra-platform-at-monday-com-4483388052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior GPU Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zesty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-gpu-platform-engineer-at-zesty-4481405125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobgether</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-at-jobgether-4480437632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principal DevOps Engineer - AI Platforms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-ai-platforms-at-palo-alto-networks-4471749164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-alice-formerly-activefence-4472729462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Platform Engineer (Mid-level)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-mid-level-at-jobgether-4481691238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guesty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-platform-engineer-at-guesty-4473205757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DoiT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-doit-4463987032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Infrastructure &amp; Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moon Active</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-cloud-engineer-at-moon-active-4447031167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-engineer-at-cato-networks-4463471007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-infrastructure-engineer-at-moveo-source-4480775799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer (37823)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-37823-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4482463663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Administrator (1007969)</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-administrator-1007969-at-elad-software-systems-4482089049</t>
   </si>
   <si>
@@ -1044,12 +1062,6 @@
     <t xml:space="preserve">Octally Integration</t>
   </si>
   <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-administrator-cloud-microsoft-infrastructure-at-octally-integration-4480045453</t>
   </si>
   <si>
@@ -1119,33 +1131,33 @@
     <t xml:space="preserve">AWS</t>
   </si>
   <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
     <t xml:space="preserve">Argo CD</t>
   </si>
   <si>
-    <t xml:space="preserve">GCP</t>
+    <t xml:space="preserve">Azure</t>
   </si>
   <si>
     <t xml:space="preserve">Docker</t>
   </si>
   <si>
-    <t xml:space="preserve">Azure</t>
+    <t xml:space="preserve">Python</t>
   </si>
   <si>
     <t xml:space="preserve">Terraform</t>
   </si>
   <si>
-    <t xml:space="preserve">Python</t>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAF/CDN</t>
   </si>
   <si>
     <t xml:space="preserve">Helm</t>
   </si>
   <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAF/CDN</t>
-  </si>
-  <si>
     <t xml:space="preserve">Open Roles</t>
   </si>
   <si>
@@ -1167,10 +1179,10 @@
     <t xml:space="preserve">0%</t>
   </si>
   <si>
-    <t xml:space="preserve">49.5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.5%</t>
+    <t xml:space="preserve">47.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.1%</t>
   </si>
   <si>
     <t xml:space="preserve">Role</t>
@@ -1260,15 +1272,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-hpc-systems-engineer-at-novocure-4478872342</t>
   </si>
   <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
-  </si>
-  <si>
     <t xml:space="preserve">Calanit by one</t>
   </si>
   <si>
@@ -1284,21 +1287,6 @@
     <t xml:space="preserve">2026-10-11</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior Backend &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Vault</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Cloud (any), Docker, CI/CD, Monitoring, Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-backend-devops-engineer-at-the-vault-4481056311</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior System &amp; Infrastructure Engineer</t>
   </si>
   <si>
@@ -1338,7 +1326,7 @@
     <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4471963869</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4471977303</t>
   </si>
   <si>
     <t xml:space="preserve">Cloud Monitoring Engineer (Student Position)</t>
@@ -1428,12 +1416,6 @@
     <t xml:space="preserve">2026-10-16</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, Cloud (any), Networking, Active Directory, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-medulla-4468207460</t>
-  </si>
-  <si>
     <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
   </si>
   <si>
@@ -1446,6 +1428,39 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
   </si>
   <si>
+    <t xml:space="preserve">Linux System Administrator (37866)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-37866-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4483535843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator Tier 3 – IT Infrastructure &amp; Cybersecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mornex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-tier-3-%E2%80%93-it-infrastructure-cybersecurity-at-mornex-4474264582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Network Operations Center</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Monitoring, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-operations-center-at-compie-technologies-4483540095</t>
+  </si>
+  <si>
     <t xml:space="preserve">Junior SysAdmin / Linux</t>
   </si>
   <si>
@@ -1467,10 +1482,10 @@
     <t xml:space="preserve">Automation</t>
   </si>
   <si>
+    <t xml:space="preserve">Virtualization</t>
+  </si>
+  <si>
     <t xml:space="preserve">Terraform/IaC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory</t>
   </si>
   <si>
     <t xml:space="preserve">Elapsed (s)</t>
@@ -1622,7 +1637,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7">
@@ -1630,7 +1645,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -1638,7 +1653,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9">
@@ -1646,7 +1661,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>852</v>
+        <v>848</v>
       </c>
     </row>
     <row r="10">
@@ -1718,7 +1733,7 @@
         <v>22</v>
       </c>
       <c r="B19" s="3">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="20">
@@ -1726,7 +1741,7 @@
         <v>23</v>
       </c>
       <c r="B20" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -1745,20 +1760,20 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="B2" s="3">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="B3" s="3">
         <v>7</v>
@@ -1766,7 +1781,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="B4" s="3">
         <v>6</v>
@@ -1774,7 +1789,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="B5" s="3">
         <v>2</v>
@@ -1782,18 +1797,10 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B6" s="3">
         <v>2</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="s">
-        <v>423</v>
-      </c>
-      <c r="B7" s="3">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1803,45 +1810,45 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="1" max="1" width="17" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="B2" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="B3" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="B4" s="3">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>479</v>
+        <v>376</v>
       </c>
       <c r="B5" s="3">
         <v>24</v>
@@ -1849,7 +1856,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>373</v>
+        <v>484</v>
       </c>
       <c r="B6" s="3">
         <v>23</v>
@@ -1857,26 +1864,26 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="B7" s="3">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="B8" s="3">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="B9" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
@@ -1889,15 +1896,15 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="B11" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="B12" s="3">
         <v>12</v>
@@ -1908,31 +1915,31 @@
         <v>369</v>
       </c>
       <c r="B13" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="B14" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="B15" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="B16" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1957,13 +1964,13 @@
         <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
     </row>
     <row r="2">
@@ -1971,13 +1978,13 @@
         <v>23</v>
       </c>
       <c r="B2" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C2" s="3">
-        <v>13.4</v>
+        <v>10.4</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -1986,88 +1993,88 @@
         <v>22</v>
       </c>
       <c r="B3" s="3">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C3" s="3">
-        <v>48.8</v>
+        <v>71.9</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>9.5</v>
+        <v>8.0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>4.1</v>
+        <v>21.6</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>31.5</v>
+        <v>27.8</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>14.4</v>
+        <v>14.2</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>32.3</v>
+        <v>29.0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2079,7 +2086,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="36" customWidth="1"/>
+    <col min="2" max="2" width="45" customWidth="1"/>
     <col min="3" max="3" width="47" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -2151,7 +2158,7 @@
         <v>40</v>
       </c>
       <c r="J2" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
@@ -2183,7 +2190,7 @@
         <v>40</v>
       </c>
       <c r="J3" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
@@ -2215,7 +2222,7 @@
         <v>46</v>
       </c>
       <c r="J4" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -2247,7 +2254,7 @@
         <v>52</v>
       </c>
       <c r="J5" s="3">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6">
@@ -2279,7 +2286,7 @@
         <v>52</v>
       </c>
       <c r="J6" s="3">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7">
@@ -2311,7 +2318,7 @@
         <v>60</v>
       </c>
       <c r="J7" s="3">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8">
@@ -2343,7 +2350,7 @@
         <v>65</v>
       </c>
       <c r="J8" s="3">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9">
@@ -2375,7 +2382,7 @@
         <v>69</v>
       </c>
       <c r="J9" s="3">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10">
@@ -2407,7 +2414,7 @@
         <v>73</v>
       </c>
       <c r="J10" s="3">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11">
@@ -2439,7 +2446,7 @@
         <v>79</v>
       </c>
       <c r="J11" s="3">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12">
@@ -2471,7 +2478,7 @@
         <v>83</v>
       </c>
       <c r="J12" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -2503,7 +2510,7 @@
         <v>87</v>
       </c>
       <c r="J13" s="3">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14">
@@ -2535,7 +2542,7 @@
         <v>93</v>
       </c>
       <c r="J14" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
@@ -2567,7 +2574,7 @@
         <v>97</v>
       </c>
       <c r="J15" s="3">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -2599,7 +2606,7 @@
         <v>73</v>
       </c>
       <c r="J16" s="3">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17">
@@ -2631,7 +2638,7 @@
         <v>106</v>
       </c>
       <c r="J17" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18">
@@ -2663,7 +2670,7 @@
         <v>111</v>
       </c>
       <c r="J18" s="3">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19">
@@ -2695,7 +2702,7 @@
         <v>115</v>
       </c>
       <c r="J19" s="3">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -2725,7 +2732,7 @@
         <v>121</v>
       </c>
       <c r="J20" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -2757,7 +2764,7 @@
         <v>52</v>
       </c>
       <c r="J21" s="3">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="22">
@@ -2789,50 +2796,48 @@
         <v>65</v>
       </c>
       <c r="J22" s="3">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="C23" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="D23" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F23" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H23" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>135</v>
-      </c>
       <c r="I23" s="3" t="s">
-        <v>136</v>
+        <v>60</v>
       </c>
       <c r="J23" s="3">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>47</v>
+        <v>122</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>49</v>
@@ -2845,24 +2850,24 @@
         <v>22</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="J24" s="3">
-        <v>46</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>49</v>
@@ -2875,48 +2880,48 @@
         <v>22</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="J25" s="3">
-        <v>0</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>94</v>
+        <v>47</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>49</v>
+        <v>119</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H26" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="I26" s="3" t="s">
-        <v>145</v>
-      </c>
       <c r="J26" s="3">
-        <v>48</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>47</v>
+        <v>145</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>146</v>
@@ -2925,7 +2930,7 @@
         <v>147</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>119</v>
+        <v>148</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>42</v>
@@ -2935,18 +2940,18 @@
         <v>22</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J27" s="3">
-        <v>11</v>
+        <v>62</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>150</v>
+        <v>94</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>151</v>
@@ -2955,28 +2960,28 @@
         <v>152</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>153</v>
+        <v>49</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H28" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="I28" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="I28" s="3" t="s">
-        <v>155</v>
-      </c>
       <c r="J28" s="3">
-        <v>61</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>94</v>
+        <v>155</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>156</v>
@@ -2985,7 +2990,7 @@
         <v>157</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>49</v>
+        <v>158</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>37</v>
@@ -2995,27 +3000,27 @@
         <v>22</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>159</v>
+        <v>83</v>
       </c>
       <c r="J29" s="3">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B30" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>161</v>
-      </c>
       <c r="C30" s="3" t="s">
-        <v>162</v>
+        <v>133</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>163</v>
+        <v>49</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>37</v>
@@ -3025,13 +3030,13 @@
         <v>22</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>83</v>
+        <v>162</v>
       </c>
       <c r="J30" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -3039,10 +3044,10 @@
         <v>94</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>49</v>
@@ -3055,24 +3060,24 @@
         <v>22</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="J31" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>49</v>
@@ -3085,13 +3090,13 @@
         <v>22</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>69</v>
       </c>
       <c r="J32" s="3">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="33">
@@ -3099,10 +3104,10 @@
         <v>47</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>119</v>
@@ -3115,13 +3120,13 @@
         <v>22</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="J33" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
@@ -3129,10 +3134,10 @@
         <v>47</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>49</v>
@@ -3145,13 +3150,13 @@
         <v>22</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="J34" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35">
@@ -3159,10 +3164,10 @@
         <v>94</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>49</v>
@@ -3175,84 +3180,84 @@
         <v>22</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="I35" s="3" t="s">
         <v>83</v>
       </c>
       <c r="J35" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>47</v>
+        <v>178</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H36" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="I36" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="I36" s="3" t="s">
-        <v>182</v>
-      </c>
       <c r="J36" s="3">
-        <v>32</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="J37" s="3">
-        <v>8</v>
+        <v>26</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>49</v>
@@ -3265,120 +3270,120 @@
         <v>22</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>189</v>
+        <v>172</v>
       </c>
       <c r="J38" s="3">
-        <v>25</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>190</v>
+        <v>94</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>174</v>
+        <v>40</v>
       </c>
       <c r="J39" s="3">
-        <v>3</v>
+        <v>28</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>94</v>
+        <v>190</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>138</v>
+        <v>192</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="J40" s="3">
-        <v>27</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B41" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="C41" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="C41" s="3" t="s">
-        <v>197</v>
-      </c>
       <c r="D41" s="3" t="s">
-        <v>49</v>
+        <v>119</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H41" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="I41" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>83</v>
-      </c>
       <c r="J41" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>47</v>
+        <v>199</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>199</v>
+        <v>167</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3" t="s">
@@ -3388,24 +3393,24 @@
         <v>200</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>46</v>
+        <v>198</v>
       </c>
       <c r="J42" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B43" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="C43" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="C43" s="3" t="s">
+      <c r="D43" s="3" t="s">
         <v>203</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>119</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>37</v>
@@ -3418,24 +3423,24 @@
         <v>204</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>205</v>
+        <v>83</v>
       </c>
       <c r="J43" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>94</v>
+        <v>205</v>
       </c>
       <c r="B44" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="C44" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="D44" s="3" t="s">
         <v>207</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>208</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>37</v>
@@ -3445,10 +3450,10 @@
         <v>22</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>83</v>
+        <v>165</v>
       </c>
       <c r="J44" s="3">
         <v>0</v>
@@ -3456,43 +3461,43 @@
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>210</v>
+        <v>47</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>169</v>
+        <v>209</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>157</v>
+        <v>133</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>205</v>
+        <v>144</v>
       </c>
       <c r="J45" s="3">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B46" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="B46" s="3" t="s">
-        <v>213</v>
-      </c>
       <c r="C46" s="3" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>49</v>
@@ -3505,30 +3510,30 @@
         <v>22</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="J46" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>47</v>
+        <v>94</v>
       </c>
       <c r="B47" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C47" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="C47" s="3" t="s">
-        <v>197</v>
-      </c>
       <c r="D47" s="3" t="s">
-        <v>49</v>
+        <v>148</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
@@ -3538,27 +3543,27 @@
         <v>216</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="J47" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>47</v>
+        <v>94</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>217</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>162</v>
+        <v>196</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>163</v>
+        <v>119</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
@@ -3568,27 +3573,27 @@
         <v>218</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>186</v>
+        <v>162</v>
       </c>
       <c r="J48" s="3">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>94</v>
+        <v>219</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>220</v>
+        <v>152</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>153</v>
+        <v>49</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
@@ -3598,10 +3603,10 @@
         <v>221</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="J49" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3612,10 +3617,10 @@
         <v>222</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>203</v>
+        <v>223</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>119</v>
+        <v>49</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>37</v>
@@ -3625,73 +3630,73 @@
         <v>22</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>167</v>
+        <v>87</v>
       </c>
       <c r="J50" s="3">
-        <v>1</v>
+        <v>43</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>94</v>
+        <v>47</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>226</v>
+        <v>165</v>
       </c>
       <c r="J51" s="3">
-        <v>63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>94</v>
+        <v>47</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>227</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>228</v>
+        <v>192</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>87</v>
+        <v>162</v>
       </c>
       <c r="J52" s="3">
-        <v>42</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -3699,10 +3704,10 @@
         <v>94</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>49</v>
@@ -3715,27 +3720,27 @@
         <v>22</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="J53" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B54" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="B54" s="3" t="s">
-        <v>202</v>
-      </c>
       <c r="C54" s="3" t="s">
-        <v>203</v>
+        <v>152</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>119</v>
+        <v>49</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>37</v>
@@ -3748,10 +3753,10 @@
         <v>233</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>205</v>
+        <v>165</v>
       </c>
       <c r="J54" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3759,70 +3764,70 @@
         <v>234</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>235</v>
+        <v>195</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>119</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>238</v>
+        <v>198</v>
       </c>
       <c r="J55" s="3">
-        <v>22</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>157</v>
+        <v>238</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>49</v>
+        <v>119</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F56" s="3"/>
       <c r="G56" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>83</v>
+        <v>240</v>
       </c>
       <c r="J56" s="3">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>94</v>
+        <v>241</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>242</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>49</v>
@@ -3841,21 +3846,21 @@
         <v>83</v>
       </c>
       <c r="J57" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B58" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="B58" s="3" t="s">
-        <v>245</v>
-      </c>
       <c r="C58" s="3" t="s">
-        <v>203</v>
+        <v>152</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>119</v>
+        <v>49</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>37</v>
@@ -3865,24 +3870,24 @@
         <v>22</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>46</v>
+        <v>83</v>
       </c>
       <c r="J58" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="B59" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="B59" s="3" t="s">
-        <v>184</v>
-      </c>
       <c r="C59" s="3" t="s">
-        <v>138</v>
+        <v>248</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>49</v>
@@ -3890,15 +3895,17 @@
       <c r="E59" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F59" s="3"/>
+      <c r="F59" s="3" t="s">
+        <v>249</v>
+      </c>
       <c r="G59" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>83</v>
+        <v>165</v>
       </c>
       <c r="J59" s="3">
         <v>0</v>
@@ -3906,13 +3913,13 @@
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>213</v>
+        <v>179</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>49</v>
@@ -3925,30 +3932,30 @@
         <v>22</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>251</v>
+        <v>83</v>
       </c>
       <c r="J60" s="3">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>253</v>
+        <v>212</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3" t="s">
@@ -3958,21 +3965,21 @@
         <v>254</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>83</v>
+        <v>255</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>197</v>
+        <v>133</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>49</v>
@@ -3980,9 +3987,7 @@
       <c r="E62" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F62" s="3" t="s">
-        <v>257</v>
-      </c>
+      <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
         <v>22</v>
       </c>
@@ -3990,10 +3995,10 @@
         <v>258</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>174</v>
+        <v>69</v>
       </c>
       <c r="J62" s="3">
-        <v>3</v>
+        <v>68</v>
       </c>
     </row>
     <row r="63">
@@ -4001,10 +4006,10 @@
         <v>259</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>169</v>
+        <v>260</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>49</v>
@@ -4017,27 +4022,27 @@
         <v>22</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>145</v>
+        <v>262</v>
       </c>
       <c r="J63" s="3">
-        <v>48</v>
+        <v>21</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>224</v>
+        <v>264</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>138</v>
+        <v>215</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>49</v>
+        <v>148</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>37</v>
@@ -4047,57 +4052,57 @@
         <v>22</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>69</v>
+        <v>144</v>
       </c>
       <c r="J64" s="3">
-        <v>67</v>
+        <v>12</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>266</v>
+        <v>162</v>
       </c>
       <c r="J65" s="3">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>268</v>
+        <v>179</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>220</v>
+        <v>133</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>153</v>
+        <v>49</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>37</v>
@@ -4107,40 +4112,40 @@
         <v>22</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="J66" s="3">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>157</v>
+        <v>196</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>49</v>
+        <v>119</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>167</v>
+        <v>83</v>
       </c>
       <c r="J67" s="3">
         <v>1</v>
@@ -4148,16 +4153,16 @@
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>49</v>
+        <v>148</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>37</v>
@@ -4167,57 +4172,57 @@
         <v>22</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>174</v>
+        <v>83</v>
       </c>
       <c r="J68" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>184</v>
+        <v>278</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
       <c r="J69" s="3">
-        <v>1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>203</v>
+        <v>133</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>119</v>
+        <v>49</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>42</v>
@@ -4227,27 +4232,27 @@
         <v>22</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>83</v>
+        <v>162</v>
       </c>
       <c r="J70" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>152</v>
+        <v>192</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>153</v>
+        <v>49</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>37</v>
@@ -4257,24 +4262,24 @@
         <v>22</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>83</v>
+        <v>198</v>
       </c>
       <c r="J71" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>49</v>
@@ -4287,84 +4292,84 @@
         <v>22</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>189</v>
+        <v>83</v>
       </c>
       <c r="J72" s="3">
-        <v>25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="J73" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>197</v>
+        <v>133</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>205</v>
+        <v>83</v>
       </c>
       <c r="J74" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>294</v>
+        <v>167</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>49</v>
@@ -4377,57 +4382,57 @@
         <v>22</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>83</v>
+        <v>297</v>
       </c>
       <c r="J75" s="3">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="I76" s="3" t="s">
         <v>83</v>
       </c>
       <c r="J76" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>301</v>
+        <v>192</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>119</v>
+        <v>49</v>
       </c>
       <c r="E77" s="3" t="s">
         <v>37</v>
@@ -4440,10 +4445,10 @@
         <v>302</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>46</v>
+        <v>262</v>
       </c>
       <c r="J77" s="3">
-        <v>6</v>
+        <v>21</v>
       </c>
     </row>
     <row r="78">
@@ -4451,46 +4456,46 @@
         <v>303</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>169</v>
+        <v>304</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>138</v>
+        <v>305</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>49</v>
+        <v>119</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>305</v>
+        <v>162</v>
       </c>
       <c r="J78" s="3">
-        <v>26</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>306</v>
+        <v>116</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>307</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>197</v>
+        <v>133</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
@@ -4500,10 +4505,10 @@
         <v>308</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>266</v>
+        <v>40</v>
       </c>
       <c r="J79" s="3">
-        <v>20</v>
+        <v>28</v>
       </c>
     </row>
     <row r="80">
@@ -4511,193 +4516,193 @@
         <v>309</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>301</v>
+        <v>248</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>119</v>
+        <v>49</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="J80" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>116</v>
+        <v>312</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>40</v>
+        <v>315</v>
       </c>
       <c r="J81" s="3">
-        <v>27</v>
+        <v>88</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>53</v>
+        <v>316</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>301</v>
+        <v>152</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>119</v>
+        <v>49</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>315</v>
+        <v>60</v>
       </c>
       <c r="J82" s="3">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>316</v>
+        <v>53</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>138</v>
+        <v>305</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>49</v>
+        <v>119</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="J83" s="3">
-        <v>87</v>
+        <v>44</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>157</v>
+        <v>324</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>49</v>
+        <v>119</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>60</v>
+        <v>175</v>
       </c>
       <c r="J84" s="3">
-        <v>46</v>
+        <v>6</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>274</v>
+        <v>327</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>324</v>
+        <v>248</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>119</v>
+        <v>49</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F85" s="3"/>
       <c r="G85" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>177</v>
+        <v>262</v>
       </c>
       <c r="J85" s="3">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>327</v>
+        <v>163</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>119</v>
+        <v>49</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>37</v>
@@ -4707,119 +4712,119 @@
         <v>22</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="J86" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>245</v>
+        <v>332</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="D87" s="3" t="s">
         <v>119</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F87" s="3"/>
       <c r="G87" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="J87" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>268</v>
+        <v>335</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="D88" s="3" t="s">
         <v>119</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F88" s="3" t="s">
-        <v>332</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="F88" s="3"/>
       <c r="G88" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="J88" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>335</v>
+        <v>264</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>157</v>
+        <v>196</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>49</v>
+        <v>119</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F89" s="3"/>
+      <c r="F89" s="3" t="s">
+        <v>338</v>
+      </c>
       <c r="G89" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="J89" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>268</v>
+        <v>341</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>203</v>
+        <v>152</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>119</v>
+        <v>49</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>37</v>
@@ -4829,84 +4834,84 @@
         <v>22</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>83</v>
+        <v>175</v>
       </c>
       <c r="J90" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>340</v>
+        <v>264</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>341</v>
+        <v>196</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>342</v>
+        <v>119</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F91" s="3"/>
       <c r="G91" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>174</v>
+        <v>83</v>
       </c>
       <c r="J91" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>157</v>
+        <v>206</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>49</v>
+        <v>207</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F92" s="3"/>
       <c r="G92" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>83</v>
+        <v>172</v>
       </c>
       <c r="J92" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="D93" s="3" t="s">
         <v>49</v>
@@ -4919,27 +4924,27 @@
         <v>22</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>177</v>
+        <v>83</v>
       </c>
       <c r="J93" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>203</v>
+        <v>152</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>119</v>
+        <v>49</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>37</v>
@@ -4949,30 +4954,30 @@
         <v>22</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="J94" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>355</v>
+        <v>196</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>153</v>
+        <v>119</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F95" s="3"/>
       <c r="G95" s="3" t="s">
@@ -4982,10 +4987,10 @@
         <v>356</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>83</v>
+        <v>162</v>
       </c>
       <c r="J95" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96">
@@ -4999,14 +5004,12 @@
         <v>359</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>119</v>
+        <v>148</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>332</v>
-      </c>
+      <c r="F96" s="3"/>
       <c r="G96" s="3" t="s">
         <v>22</v>
       </c>
@@ -5017,11 +5020,43 @@
         <v>83</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F97" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="G97" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H97" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="I97" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="J97" s="3">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J96"/>
+  <autoFilter ref="A1:J97"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5118,6 +5153,7 @@
     <hyperlink ref="H94" r:id="rId93"/>
     <hyperlink ref="H95" r:id="rId94"/>
     <hyperlink ref="H96" r:id="rId95"/>
+    <hyperlink ref="H97" r:id="rId96"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5125,9 +5161,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="48" customWidth="1"/>
-    <col min="2" max="2" width="36" customWidth="1"/>
-    <col min="3" max="3" width="46" customWidth="1"/>
+    <col min="1" max="1" width="35" customWidth="1"/>
+    <col min="2" max="2" width="45" customWidth="1"/>
+    <col min="3" max="3" width="44" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
@@ -5159,32 +5195,32 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>75</v>
+        <v>163</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>82</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>122</v>
+        <v>205</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>140</v>
+        <v>163</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>141</v>
+        <v>206</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -5192,18 +5228,18 @@
         <v>22</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>142</v>
+        <v>208</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>160</v>
+        <v>219</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>161</v>
+        <v>220</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -5211,18 +5247,18 @@
         <v>22</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>164</v>
+        <v>221</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>94</v>
+        <v>47</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>178</v>
+        <v>225</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5230,18 +5266,18 @@
         <v>22</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>179</v>
+        <v>226</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>195</v>
+        <v>231</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>197</v>
+        <v>152</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -5249,18 +5285,18 @@
         <v>22</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>198</v>
+        <v>233</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>94</v>
+        <v>246</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>206</v>
+        <v>247</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>207</v>
+        <v>248</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -5268,18 +5304,18 @@
         <v>22</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>209</v>
+        <v>250</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>239</v>
+        <v>289</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>240</v>
+        <v>290</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>157</v>
+        <v>133</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -5287,18 +5323,18 @@
         <v>22</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>241</v>
+        <v>291</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>94</v>
+        <v>309</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>242</v>
+        <v>310</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>157</v>
+        <v>248</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -5306,18 +5342,18 @@
         <v>22</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>243</v>
+        <v>311</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>247</v>
+        <v>329</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>184</v>
+        <v>163</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>138</v>
+        <v>192</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -5325,182 +5361,11 @@
         <v>22</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>360</v>
+        <v>330</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G19"/>
+  <autoFilter ref="A1:G10"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -5511,15 +5376,6 @@
     <hyperlink ref="G8" r:id="rId7"/>
     <hyperlink ref="G9" r:id="rId8"/>
     <hyperlink ref="G10" r:id="rId9"/>
-    <hyperlink ref="G11" r:id="rId10"/>
-    <hyperlink ref="G12" r:id="rId11"/>
-    <hyperlink ref="G13" r:id="rId12"/>
-    <hyperlink ref="G14" r:id="rId13"/>
-    <hyperlink ref="G15" r:id="rId14"/>
-    <hyperlink ref="G16" r:id="rId15"/>
-    <hyperlink ref="G17" r:id="rId16"/>
-    <hyperlink ref="G18" r:id="rId17"/>
-    <hyperlink ref="G19" r:id="rId18"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5533,39 +5389,39 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="B2" s="3">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="B3" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>257</v>
+        <v>369</v>
       </c>
       <c r="B4" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>365</v>
+        <v>249</v>
       </c>
       <c r="B5" s="3">
         <v>14</v>
@@ -5573,7 +5429,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="B6" s="3">
         <v>9</v>
@@ -5581,23 +5437,23 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B7" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="B8" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B9" s="3">
         <v>8</v>
@@ -5605,7 +5461,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="B10" s="3">
         <v>8</v>
@@ -5621,7 +5477,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B12" s="3">
         <v>7</v>
@@ -5629,15 +5485,15 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B13" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="B14" s="3">
         <v>6</v>
@@ -5645,7 +5501,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="B15" s="3">
         <v>6</v>
@@ -5653,10 +5509,10 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="B16" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -5666,7 +5522,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="23" customWidth="1"/>
+    <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5675,20 +5531,20 @@
         <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>169</v>
+        <v>34</v>
       </c>
       <c r="B2" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="B3" s="3">
         <v>3</v>
@@ -5696,7 +5552,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="B4" s="3">
         <v>3</v>
@@ -5704,7 +5560,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -5712,7 +5568,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>89</v>
+        <v>163</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -5720,7 +5576,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>184</v>
+        <v>167</v>
       </c>
       <c r="B7" s="3">
         <v>3</v>
@@ -5728,7 +5584,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>268</v>
+        <v>179</v>
       </c>
       <c r="B8" s="3">
         <v>3</v>
@@ -5736,15 +5592,15 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>48</v>
+        <v>264</v>
       </c>
       <c r="B9" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>108</v>
+        <v>48</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -5752,7 +5608,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>171</v>
+        <v>108</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5760,7 +5616,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>202</v>
+        <v>169</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5768,7 +5624,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>213</v>
+        <v>195</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5776,7 +5632,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -5784,18 +5640,18 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>245</v>
+        <v>56</v>
       </c>
       <c r="B15" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>274</v>
+        <v>102</v>
       </c>
       <c r="B16" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -5806,23 +5662,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="23" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="2">
@@ -5900,13 +5756,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C7" s="3">
-        <v>5.6</v>
+        <v>4.2</v>
       </c>
       <c r="D7" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -5914,7 +5770,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="C8" s="3">
         <v>4.2</v>
@@ -5928,7 +5784,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="C9" s="3">
         <v>4.0</v>
@@ -5956,13 +5812,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>56</v>
+        <v>163</v>
       </c>
       <c r="C11" s="3">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="D11" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -5970,13 +5826,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>245</v>
+        <v>56</v>
       </c>
       <c r="C12" s="3">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="D12" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -5984,13 +5840,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>274</v>
+        <v>123</v>
       </c>
       <c r="C13" s="3">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="D13" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -5998,13 +5854,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>123</v>
+        <v>169</v>
       </c>
       <c r="C14" s="3">
         <v>2.4</v>
       </c>
       <c r="D14" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -6012,7 +5868,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>171</v>
+        <v>195</v>
       </c>
       <c r="C15" s="3">
         <v>2.4</v>
@@ -6026,7 +5882,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="C16" s="3">
         <v>2.4</v>
@@ -6052,21 +5908,21 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="B2" s="3">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="3">
@@ -6074,10 +5930,10 @@
         <v>37</v>
       </c>
       <c r="B3" s="3">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="4">
@@ -6085,10 +5941,10 @@
         <v>42</v>
       </c>
       <c r="B4" s="3">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
     </row>
   </sheetData>
@@ -6107,7 +5963,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
     </row>
     <row r="2">
@@ -6115,7 +5971,7 @@
         <v>49</v>
       </c>
       <c r="B2" s="3">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3">
@@ -6123,12 +5979,12 @@
         <v>119</v>
       </c>
       <c r="B3" s="3">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="B4" s="3">
         <v>5</v>
@@ -6144,7 +6000,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>163</v>
+        <v>207</v>
       </c>
       <c r="B6" s="3">
         <v>2</v>
@@ -6160,7 +6016,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>208</v>
+        <v>158</v>
       </c>
       <c r="B8" s="3">
         <v>1</v>
@@ -6168,7 +6024,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>342</v>
+        <v>203</v>
       </c>
       <c r="B9" s="3">
         <v>1</v>
@@ -6183,7 +6039,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="32" customWidth="1"/>
+    <col min="3" max="3" width="34" customWidth="1"/>
     <col min="4" max="4" width="44" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -6195,10 +6051,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>25</v>
@@ -6210,10 +6066,10 @@
         <v>27</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>20</v>
@@ -6230,7 +6086,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>56</v>
@@ -6239,22 +6095,22 @@
         <v>57</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
     </row>
     <row r="3">
@@ -6262,31 +6118,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
     </row>
     <row r="4">
@@ -6294,28 +6150,28 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>69</v>
@@ -6326,28 +6182,28 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="F5" s="3">
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>69</v>
@@ -6358,31 +6214,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="F6" s="3">
         <v>100</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7">
@@ -6390,31 +6246,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>413</v>
+        <v>337</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>224</v>
+        <v>417</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>138</v>
+        <v>418</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="F7" s="3">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>305</v>
+        <v>421</v>
       </c>
     </row>
     <row r="8">
@@ -6422,31 +6278,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>331</v>
+        <v>422</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>394</v>
+        <v>425</v>
       </c>
       <c r="F8" s="3">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
     </row>
     <row r="9">
@@ -6454,31 +6310,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>301</v>
+        <v>206</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>423</v>
+        <v>398</v>
       </c>
       <c r="F9" s="3">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>167</v>
+        <v>255</v>
       </c>
     </row>
     <row r="10">
@@ -6486,31 +6342,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>427</v>
+        <v>169</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>428</v>
+        <v>170</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>429</v>
+        <v>398</v>
       </c>
       <c r="F10" s="3">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>432</v>
+        <v>297</v>
       </c>
     </row>
     <row r="11">
@@ -6518,31 +6374,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>341</v>
+        <v>192</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>394</v>
+        <v>405</v>
       </c>
       <c r="F11" s="3">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>251</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12">
@@ -6550,31 +6406,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>171</v>
+        <v>441</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>157</v>
+        <v>133</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="F12" s="3">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>174</v>
+        <v>444</v>
       </c>
     </row>
     <row r="13">
@@ -6582,31 +6438,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="F13" s="3">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>93</v>
+        <v>297</v>
       </c>
     </row>
     <row r="14">
@@ -6614,31 +6470,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>138</v>
+        <v>215</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>394</v>
+        <v>405</v>
       </c>
       <c r="F14" s="3">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>448</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -6646,31 +6502,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>441</v>
+        <v>403</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>197</v>
+        <v>404</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="F15" s="3">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>305</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16">
@@ -6678,31 +6534,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>220</v>
+        <v>457</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="F16" s="3">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>69</v>
+        <v>460</v>
       </c>
     </row>
     <row r="17">
@@ -6710,31 +6566,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>399</v>
+        <v>214</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>400</v>
+        <v>196</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="F17" s="3">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>121</v>
+        <v>464</v>
       </c>
     </row>
     <row r="18">
@@ -6742,31 +6598,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>461</v>
+        <v>133</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="F18" s="3">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>464</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19">
@@ -6774,31 +6630,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>219</v>
+        <v>332</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="F19" s="3">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>468</v>
+        <v>83</v>
       </c>
     </row>
     <row r="20">
@@ -6806,31 +6662,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>465</v>
+        <v>472</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>242</v>
+        <v>473</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>207</v>
+        <v>474</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="F20" s="3">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
     </row>
     <row r="21">
@@ -6838,31 +6694,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>472</v>
+        <v>267</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>388</v>
+        <v>398</v>
       </c>
       <c r="F21" s="3">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W44.xlsx
+++ b/reports/devops-jobs-israel-2026-W44.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="498">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="507">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-27T11:59:45</t>
+    <t xml:space="preserve">2026-10-28T12:39:34</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -219,6 +219,18 @@
     <t xml:space="preserve">2026-08-31</t>
   </si>
   <si>
+    <t xml:space="preserve">Observability Platform Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Postgres, MongoDB, Redis, Kafka, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4714074006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-28</t>
+  </si>
+  <si>
     <t xml:space="preserve">Senior DevSecOps Manager</t>
   </si>
   <si>
@@ -528,6 +540,12 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-devops-engineer-cortex-cloud-at-palo-alto-networks-4443693726</t>
   </si>
   <si>
+    <t xml:space="preserve">Logica-IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-logica-it-4482293600</t>
+  </si>
+  <si>
     <t xml:space="preserve">NVIDIA</t>
   </si>
   <si>
@@ -540,925 +558,934 @@
     <t xml:space="preserve">2026-10-23</t>
   </si>
   <si>
-    <t xml:space="preserve">Fullpath</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fullpath-4480776925</t>
+    <t xml:space="preserve">BigID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-bigid-4482680687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer - Cloud Infra Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-infra-team-at-wix-4480881694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer, AIOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-aiops-at-nvidia-4471970512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer and SRE Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upstream Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-and-sre-lead-at-upstream-security-4482467626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Devops Engineer - AI Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bridgewise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-ai-team-at-bridgewise-4482680803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform DevOps Engineer - Core Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jeen.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-devops-engineer-core-platform-at-jeen-ai-4482092082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experienced DevOps Engineer (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/experienced-devops-engineer-cortex-at-palo-alto-networks-4462513797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Speedata.io</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-speedata-io-4483379335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-engineer-at-comblack-4483582140</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zenity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-zenity-4478465745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4481079700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SR DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bitsight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-bitsight-4483570331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personetics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-personetics-4428829912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeValue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-codevalue-4483726365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elementor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-elementor-4482868447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pontera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-pontera-4481315450</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-sqlink-group-4482292829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Webiks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-reliability-engineer-at-webiks-4483579517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-devops-engineer-at-jeen-ai-4482082697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Software Engineer, DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aiven</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-software-engineer-devops-at-aiven-4426867332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Founding DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stealth-Mode Cybersecurity Startup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/founding-devops-at-stealth-mode-cybersecurity-startup-4482932513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Data Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-data-infrastructure-engineer-at-evoke-4462157157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SciPlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-sciplay-4391151881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevSecOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PayPlus - The Future of Payments &amp; Commerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devsecops-engineer-at-payplus-the-future-of-payments-commerce-4482999139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Tech Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-wix-4483537365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claroty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-claroty-4482292784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oriient</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-oriient-4484447442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineering - Storage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineering-storage-at-nvidia-4457190574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. SRE AI Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Navan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-sre-ai-engineer-at-navan-4437742346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/observability-platform-team-lead-at-gong-4484452499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure Engineer - Core Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-core-systems-at-wix-4483368404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infra Engineer Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infra-engineer-team-lead-at-dialog-4481085538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software System Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-system-reliability-engineer-at-cisco-4483388333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Backend Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akamai Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-backend-infrastructure-engineer-at-akamai-technologies-4473769865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Software Engineer -Platform Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viz.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-software-engineer-platform-team-at-viz-ai-4437383686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Immunai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-immunai-4482405033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sunbit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-sunbit-4484439423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Platform Engineer (Infra Platform)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">monday.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-infra-platform-at-monday-com-4483388052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ScaleOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-scaleops-4483763089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior GPU Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zesty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-gpu-platform-engineer-at-zesty-4481405125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI &amp; Software Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BioCatch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-software-infra-engineer-at-biocatch-4447894244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Millennium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-millennium-4482698329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-alice-formerly-activefence-4472729462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Platform Engineer (Mid-level)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobgether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-mid-level-at-jobgether-4481691238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OpenShift Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential Careers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/openshift-platform-engineer-at-confidential-careers-4482299668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Agentic AI Engineer (AWS/DevOps)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Directeam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-agentic-ai-engineer-aws-devops-at-directeam-4482501198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal Data Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MediaForce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-data-platform-engineer-at-mediaforce-4481460917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Infrastructure &amp; Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moon Active</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-cloud-engineer-at-moon-active-4447031167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calanit by one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-calanit-by-one-4484447830</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure Infrastructure Engineer – AI &amp; Automation (5524)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INGIMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/azure-infrastructure-engineer-%E2%80%93-ai-automation-5524-at-ingima-4484427543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT DevOps Engineer - 244284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-devops-engineer-244284-at-experis-israel-4482290223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integress, Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-engineer-at-integress-inc-4483842402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-engineer-at-cato-networks-4463471007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal Devops &amp; Infra Tech Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-infra-tech-lead-at-sunbit-4474134295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Integration &amp; Infrastructure Engineer (Advanced storage infrastructure for AI workloads)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sandisk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-integration-infrastructure-engineer-advanced-storage-infrastructure-for-ai-workloads-at-sandisk-4478351208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moveo Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-infrastructure-engineer-at-moveo-source-4480775799</t>
   </si>
   <si>
     <t xml:space="preserve">2026-10-21</t>
   </si>
   <si>
-    <t xml:space="preserve">BigID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-bigid-4482680687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer - Cloud Infra Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-infra-team-at-wix-4480881694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer, AIOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-aiops-at-nvidia-4471970512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer and SRE Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upstream Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-and-sre-lead-at-upstream-security-4482467626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">At-Bay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-at-bay-4471503422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Devops Engineer - AI Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bridgewise</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-ai-team-at-bridgewise-4482680803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform DevOps Engineer - Core Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jeen.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-devops-engineer-core-platform-at-jeen-ai-4482092082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experienced DevOps Engineer (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/experienced-devops-engineer-cortex-at-palo-alto-networks-4462513797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Speedata.io</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-speedata-io-4483379335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-engineer-at-comblack-4483582140</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zenity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-zenity-4478465745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps / Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lendbuzz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-site-reliability-engineer-sre-at-lendbuzz-4480488912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-abra-4480795007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4481079700</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SR DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bitsight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-bitsight-4483570331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Personetics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-personetics-4428829912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeValue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-codevalue-4483726365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elementor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-elementor-4482868447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pontera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-pontera-4481315450</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Webiks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-reliability-engineer-at-webiks-4483579517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-devops-engineer-at-jeen-ai-4482082697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Software Engineer, DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aiven</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-software-engineer-devops-at-aiven-4426867332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Founding DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stealth-Mode Cybersecurity Startup</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/founding-devops-at-stealth-mode-cybersecurity-startup-4482932513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medulla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-medulla-4483534511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevSecOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PayPlus - The Future of Payments &amp; Commerce</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devsecops-engineer-at-payplus-the-future-of-payments-commerce-4482999139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Tech Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-wix-4483537365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-engineer-at-lendbuzz-4477980904</t>
+    <t xml:space="preserve">Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-elbit-systems-israel-4474036853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OpenShift Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/openshift-infrastructure-engineer-at-comblack-4483564559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer (37823)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-37823-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4482463663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-confidential-careers-4481088252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-infrastructure-engineer-at-logica-it-4481435276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft System Administrator (5515)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-administrator-5515-at-ingima-4483376293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E2E Solutions IL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-e2e-solutions-il-4482928669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JobsSeek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Midreshet Ben-Gurion, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-linux-system-administrator-at-jobsseek-4483393914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developer Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=8264438&amp;gh_jid=8264438</t>
   </si>
   <si>
     <t xml:space="preserve">2026-10-13</t>
   </si>
   <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-paragon-4456184154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. SRE AI Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-sre-ai-engineer-at-navan-4437742346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential Careers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-confidential-careers-4476662621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Integrator – SRE</t>
+    <t xml:space="preserve">Development Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clarivate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/development-operations-engineer-at-clarivate-4467992253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rapyd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux &amp; HPC Systems Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Novocure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tirat HaCarmel, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-hpc-systems-engineer-at-novocure-4478872342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-calanit-by-one-4478305717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System &amp; Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-infrastructure-engineer-at-final-4475581791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cross River</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-at-cross-river-4478788112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HPC Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4471977303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Monitoring Engineer (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-monitoring-engineer-student-position-at-upwind-security-4476759903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Technical Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New York City</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, GCP, Cloud (any), Git, Terraform/IaC, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/melio/jobs/7995568003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security Analyst (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/security-analyst-student-position-at-upwind-security-4473525994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student Software Engineer – Cloud, Big Data, Billing &amp; AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Cloud (any), Docker, Kubernetes, CI/CD, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-software-engineer-%E2%80%93-cloud-big-data-billing-ai-at-sap-4476596020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kela Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior CAD Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cad-engineer-university-graduate-google-cloud-at-google-4483213993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator (37866)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-37866-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4483535843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator Tier 3 – IT Infrastructure &amp; Cybersecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mornex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-tier-3-%E2%80%93-it-infrastructure-cybersecurity-at-mornex-4474264582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Network Operations Center</t>
   </si>
   <si>
     <t xml:space="preserve">Compie Technologies</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-integrator-%E2%80%93-sre-at-compie-technologies-4483368453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure Engineer - Core Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-core-systems-at-wix-4483368404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infra Engineer Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dialog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infra-engineer-team-lead-at-dialog-4481085538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software System Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-system-reliability-engineer-at-cisco-4483388333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Backend Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akamai Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-backend-infrastructure-engineer-at-akamai-technologies-4473769865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Software Engineer -Platform Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viz.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-software-engineer-platform-team-at-viz-ai-4437383686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Immunai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-immunai-4482405033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Platform Engineer (Infra Platform)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monday.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-infra-platform-at-monday-com-4483388052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ScaleOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-scaleops-4483763089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior GPU Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zesty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-gpu-platform-engineer-at-zesty-4481405125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principal DevOps Engineer - AI Platforms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-ai-platforms-at-palo-alto-networks-4471749164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Millennium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-millennium-4482698329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-alice-formerly-activefence-4472729462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Platform Engineer (Mid-level)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobgether</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-mid-level-at-jobgether-4481691238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guesty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-platform-engineer-at-guesty-4473205757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principal Data Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MediaForce</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-data-platform-engineer-at-mediaforce-4481460917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Infrastructure &amp; Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moon Active</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-cloud-engineer-at-moon-active-4447031167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-engineer-at-cato-networks-4463471007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DoiT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-doit-4463987032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moveo Source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-infrastructure-engineer-at-moveo-source-4480775799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-elbit-systems-israel-4474036853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OpenShift Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/openshift-infrastructure-engineer-at-comblack-4483564559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer (37823)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-37823-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4482463663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Administrator (1007969)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elad Software Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-administrator-1007969-at-elad-software-systems-4482089049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-confidential-careers-4481088252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-engineer-at-comda-4478983773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Application Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/application-infrastructure-engineer-at-confidential-careers-4481082731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Administrator - Cloud, Microsoft &amp; Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Octally Integration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-administrator-cloud-microsoft-infrastructure-at-octally-integration-4480045453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logica-IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-infrastructure-engineer-at-logica-it-4481435276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure Engineer (10296)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bynet Data Communications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-10296-at-bynet-data-communications-4478972863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft System Administrator (5515)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INGIMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-administrator-5515-at-ingima-4483376293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E2E Solutions IL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-e2e-solutions-il-4482928669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JobsSeek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Midreshet Ben-Gurion, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-linux-system-administrator-at-jobsseek-4483393914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.9%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developer Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=8264438&amp;gh_jid=8264438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Development Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clarivate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/development-operations-engineer-at-clarivate-4467992253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rapyd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux &amp; HPC Systems Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Novocure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tirat HaCarmel, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-hpc-systems-engineer-at-novocure-4478872342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calanit by one</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-calanit-by-one-4478305717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System &amp; Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-infrastructure-engineer-at-final-4475581791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cross River</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-at-cross-river-4478788112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HPC Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4471977303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Monitoring Engineer (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upwind Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-monitoring-engineer-student-position-at-upwind-security-4476759903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Technical Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security Analyst (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/security-analyst-student-position-at-upwind-security-4473525994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Integration Student, SPIV team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Annapurna Labs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-integration-student-spiv-team-at-annapurna-labs-4456348779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student Software Engineer – Cloud, Big Data, Billing &amp; AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Cloud (any), Docker, Kubernetes, CI/CD, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-software-engineer-%E2%80%93-cloud-big-data-billing-ai-at-sap-4476596020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, Cloud (any), Networking, Active Directory, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-abra-4467537853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kela Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator (37866)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-37866-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4483535843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator Tier 3 – IT Infrastructure &amp; Cybersecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mornex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-tier-3-%E2%80%93-it-infrastructure-cybersecurity-at-mornex-4474264582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Network Operations Center</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Monitoring, Virtualization</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-operations-center-at-compie-technologies-4483540095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnCloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
   </si>
   <si>
     <t xml:space="preserve">Junior SysAdmin / Linux</t>
@@ -1637,7 +1664,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7">
@@ -1645,7 +1672,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -1653,7 +1680,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9">
@@ -1661,7 +1688,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>848</v>
+        <v>844</v>
       </c>
     </row>
     <row r="10">
@@ -1733,7 +1760,7 @@
         <v>22</v>
       </c>
       <c r="B19" s="3">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="20">
@@ -1741,7 +1768,7 @@
         <v>23</v>
       </c>
       <c r="B20" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -1760,20 +1787,20 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="B2" s="3">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="B3" s="3">
         <v>7</v>
@@ -1781,7 +1808,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>392</v>
+        <v>439</v>
       </c>
       <c r="B4" s="3">
         <v>6</v>
@@ -1792,12 +1819,12 @@
         <v>425</v>
       </c>
       <c r="B5" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>480</v>
+        <v>489</v>
       </c>
       <c r="B6" s="3">
         <v>2</v>
@@ -1816,47 +1843,47 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>481</v>
+        <v>490</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>338</v>
+        <v>491</v>
       </c>
       <c r="B2" s="3">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>482</v>
+        <v>359</v>
       </c>
       <c r="B3" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>483</v>
+        <v>492</v>
       </c>
       <c r="B4" s="3">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>376</v>
+        <v>493</v>
       </c>
       <c r="B5" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>484</v>
+        <v>382</v>
       </c>
       <c r="B6" s="3">
         <v>23</v>
@@ -1864,15 +1891,15 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="B7" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>485</v>
+        <v>494</v>
       </c>
       <c r="B8" s="3">
         <v>17</v>
@@ -1880,7 +1907,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>486</v>
+        <v>495</v>
       </c>
       <c r="B9" s="3">
         <v>17</v>
@@ -1888,15 +1915,15 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="B10" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="B11" s="3">
         <v>12</v>
@@ -1904,39 +1931,39 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>373</v>
+        <v>328</v>
       </c>
       <c r="B12" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>369</v>
+        <v>315</v>
       </c>
       <c r="B13" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="B14" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>487</v>
+        <v>496</v>
       </c>
       <c r="B15" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>488</v>
+        <v>497</v>
       </c>
       <c r="B16" s="3">
         <v>7</v>
@@ -1964,13 +1991,13 @@
         <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>489</v>
+        <v>498</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>490</v>
+        <v>499</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>491</v>
+        <v>500</v>
       </c>
     </row>
     <row r="2">
@@ -1978,13 +2005,13 @@
         <v>23</v>
       </c>
       <c r="B2" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" s="3">
-        <v>10.4</v>
+        <v>12.1</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>492</v>
+        <v>501</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -1996,85 +2023,85 @@
         <v>79</v>
       </c>
       <c r="C3" s="3">
-        <v>71.9</v>
+        <v>36.9</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>492</v>
+        <v>501</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>493</v>
+        <v>502</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>8.0</v>
+        <v>7.9</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>492</v>
+        <v>501</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>494</v>
+        <v>503</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>21.6</v>
+        <v>2.7</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>492</v>
+        <v>501</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>495</v>
+        <v>504</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>27.8</v>
+        <v>32.2</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>492</v>
+        <v>501</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>496</v>
+        <v>505</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>14.2</v>
+        <v>18.5</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>492</v>
+        <v>501</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>497</v>
+        <v>506</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>29.0</v>
+        <v>29.9</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>492</v>
+        <v>501</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2158,7 +2185,7 @@
         <v>40</v>
       </c>
       <c r="J2" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
@@ -2190,7 +2217,7 @@
         <v>40</v>
       </c>
       <c r="J3" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">
@@ -2222,7 +2249,7 @@
         <v>46</v>
       </c>
       <c r="J4" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -2254,7 +2281,7 @@
         <v>52</v>
       </c>
       <c r="J5" s="3">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6">
@@ -2286,7 +2313,7 @@
         <v>52</v>
       </c>
       <c r="J6" s="3">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7">
@@ -2318,7 +2345,7 @@
         <v>60</v>
       </c>
       <c r="J7" s="3">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8">
@@ -2350,7 +2377,7 @@
         <v>65</v>
       </c>
       <c r="J8" s="3">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9">
@@ -2382,7 +2409,7 @@
         <v>69</v>
       </c>
       <c r="J9" s="3">
-        <v>68</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -2414,7 +2441,7 @@
         <v>73</v>
       </c>
       <c r="J10" s="3">
-        <v>61</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11">
@@ -2422,10 +2449,10 @@
         <v>74</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>49</v>
@@ -2434,30 +2461,30 @@
         <v>42</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="J11" s="3">
-        <v>40</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>80</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>76</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>49</v>
@@ -2478,7 +2505,7 @@
         <v>83</v>
       </c>
       <c r="J12" s="3">
-        <v>1</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13">
@@ -2486,16 +2513,16 @@
         <v>84</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>85</v>
@@ -2510,7 +2537,7 @@
         <v>87</v>
       </c>
       <c r="J13" s="3">
-        <v>43</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -2518,10 +2545,10 @@
         <v>88</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>49</v>
@@ -2530,30 +2557,30 @@
         <v>37</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="J14" s="3">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>94</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>49</v>
@@ -2574,7 +2601,7 @@
         <v>97</v>
       </c>
       <c r="J15" s="3">
-        <v>71</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
@@ -2582,16 +2609,16 @@
         <v>98</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>99</v>
@@ -2603,83 +2630,83 @@
         <v>100</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="J16" s="3">
-        <v>61</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>103</v>
+        <v>49</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>42</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>106</v>
+        <v>77</v>
       </c>
       <c r="J17" s="3">
-        <v>15</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="D18" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>108</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>109</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H18" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>111</v>
-      </c>
       <c r="J18" s="3">
-        <v>67</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>108</v>
-      </c>
       <c r="C19" s="3" t="s">
         <v>49</v>
       </c>
@@ -2687,7 +2714,7 @@
         <v>49</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>113</v>
@@ -2702,7 +2729,7 @@
         <v>115</v>
       </c>
       <c r="J19" s="3">
-        <v>39</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20">
@@ -2710,98 +2737,98 @@
         <v>116</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>118</v>
+        <v>49</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>119</v>
+        <v>49</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F20" s="3"/>
+      <c r="F20" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="G20" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J20" s="3">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="D21" s="3" t="s">
         <v>123</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F21" s="3" t="s">
-        <v>125</v>
-      </c>
+      <c r="F21" s="3"/>
       <c r="G21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>52</v>
+        <v>125</v>
       </c>
       <c r="J21" s="3">
-        <v>77</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="C22" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>129</v>
-      </c>
       <c r="D22" s="3" t="s">
-        <v>119</v>
+        <v>49</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>42</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="J22" s="3">
-        <v>57</v>
+        <v>78</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>47</v>
+        <v>131</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>132</v>
@@ -2810,34 +2837,36 @@
         <v>133</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>49</v>
+        <v>123</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F23" s="3"/>
+      <c r="F23" s="3" t="s">
+        <v>134</v>
+      </c>
       <c r="G23" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="J23" s="3">
-        <v>47</v>
+        <v>58</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>122</v>
+        <v>47</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>49</v>
@@ -2850,24 +2879,24 @@
         <v>22</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="J24" s="3">
-        <v>1</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>139</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>49</v>
@@ -2880,27 +2909,27 @@
         <v>22</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>87</v>
       </c>
       <c r="J25" s="3">
-        <v>43</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>47</v>
+        <v>142</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>119</v>
+        <v>49</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>42</v>
@@ -2910,27 +2939,27 @@
         <v>22</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>144</v>
+        <v>91</v>
       </c>
       <c r="J26" s="3">
-        <v>12</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="C27" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="C27" s="3" t="s">
-        <v>147</v>
-      </c>
       <c r="D27" s="3" t="s">
-        <v>148</v>
+        <v>123</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>42</v>
@@ -2940,30 +2969,30 @@
         <v>22</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="J27" s="3">
-        <v>62</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>94</v>
+        <v>149</v>
       </c>
       <c r="B28" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="D28" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="D28" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="E28" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3" t="s">
@@ -2976,21 +3005,21 @@
         <v>154</v>
       </c>
       <c r="J28" s="3">
-        <v>13</v>
+        <v>63</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B29" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="C29" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="C29" s="3" t="s">
-        <v>157</v>
-      </c>
       <c r="D29" s="3" t="s">
-        <v>158</v>
+        <v>49</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>37</v>
@@ -3000,27 +3029,27 @@
         <v>22</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>83</v>
+        <v>158</v>
       </c>
       <c r="J29" s="3">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>94</v>
+        <v>159</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>160</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>133</v>
+        <v>161</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>49</v>
+        <v>162</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>37</v>
@@ -3030,10 +3059,10 @@
         <v>22</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>162</v>
+        <v>87</v>
       </c>
       <c r="J30" s="3">
         <v>2</v>
@@ -3041,13 +3070,13 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>49</v>
@@ -3060,30 +3089,30 @@
         <v>22</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="J31" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>166</v>
+        <v>98</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>167</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3" t="s">
@@ -3093,24 +3122,24 @@
         <v>168</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>69</v>
+        <v>169</v>
       </c>
       <c r="J32" s="3">
-        <v>68</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>47</v>
+        <v>170</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>119</v>
+        <v>49</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>42</v>
@@ -3120,13 +3149,13 @@
         <v>22</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>172</v>
+        <v>73</v>
       </c>
       <c r="J33" s="3">
-        <v>4</v>
+        <v>69</v>
       </c>
     </row>
     <row r="34">
@@ -3137,7 +3166,7 @@
         <v>173</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>133</v>
+        <v>156</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>49</v>
@@ -3153,27 +3182,27 @@
         <v>174</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>175</v>
+        <v>69</v>
       </c>
       <c r="J34" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>94</v>
+        <v>47</v>
       </c>
       <c r="B35" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="C35" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="C35" s="3" t="s">
-        <v>133</v>
-      </c>
       <c r="D35" s="3" t="s">
-        <v>49</v>
+        <v>123</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
@@ -3183,21 +3212,21 @@
         <v>177</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>83</v>
+        <v>178</v>
       </c>
       <c r="J35" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>178</v>
+        <v>98</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>179</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>49</v>
@@ -3213,27 +3242,27 @@
         <v>180</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>181</v>
+        <v>87</v>
       </c>
       <c r="J36" s="3">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B37" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>169</v>
-      </c>
       <c r="C37" s="3" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
@@ -3246,7 +3275,7 @@
         <v>184</v>
       </c>
       <c r="J37" s="3">
-        <v>26</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38">
@@ -3254,10 +3283,10 @@
         <v>185</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>49</v>
@@ -3270,54 +3299,54 @@
         <v>22</v>
       </c>
       <c r="H38" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="I38" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="I38" s="3" t="s">
-        <v>172</v>
-      </c>
       <c r="J38" s="3">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>94</v>
+        <v>188</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>40</v>
+        <v>178</v>
       </c>
       <c r="J39" s="3">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>49</v>
@@ -3330,27 +3359,27 @@
         <v>22</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="J40" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>37</v>
@@ -3360,24 +3389,24 @@
         <v>22</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="J41" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>49</v>
@@ -3390,27 +3419,27 @@
         <v>22</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="J42" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>37</v>
@@ -3420,27 +3449,27 @@
         <v>22</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="J43" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>37</v>
@@ -3450,13 +3479,13 @@
         <v>22</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="J44" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -3464,10 +3493,10 @@
         <v>47</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>49</v>
@@ -3480,30 +3509,30 @@
         <v>22</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="J45" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>211</v>
+        <v>98</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>212</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>133</v>
+        <v>197</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>49</v>
+        <v>123</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
@@ -3513,27 +3542,27 @@
         <v>213</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="J46" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>94</v>
+        <v>214</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>215</v>
+        <v>156</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>148</v>
+        <v>49</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
@@ -3543,24 +3572,24 @@
         <v>216</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="J47" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>217</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>196</v>
+        <v>218</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>119</v>
+        <v>49</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>37</v>
@@ -3570,24 +3599,24 @@
         <v>22</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>162</v>
+        <v>91</v>
       </c>
       <c r="J48" s="3">
-        <v>2</v>
+        <v>44</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>219</v>
+        <v>47</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>220</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>49</v>
@@ -3603,81 +3632,81 @@
         <v>221</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="J49" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>94</v>
+        <v>47</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>222</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>223</v>
+        <v>193</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>87</v>
+        <v>166</v>
       </c>
       <c r="J50" s="3">
-        <v>43</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>47</v>
+        <v>98</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>165</v>
+        <v>199</v>
       </c>
       <c r="J51" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>47</v>
+        <v>226</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>227</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>192</v>
+        <v>156</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>49</v>
@@ -3693,21 +3722,21 @@
         <v>228</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>162</v>
+        <v>69</v>
       </c>
       <c r="J52" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>94</v>
+        <v>229</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>49</v>
@@ -3720,27 +3749,27 @@
         <v>22</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>198</v>
+        <v>169</v>
       </c>
       <c r="J53" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>152</v>
+        <v>197</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>49</v>
+        <v>123</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>37</v>
@@ -3753,10 +3782,10 @@
         <v>233</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>165</v>
+        <v>199</v>
       </c>
       <c r="J54" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="55">
@@ -3764,70 +3793,70 @@
         <v>234</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>195</v>
+        <v>235</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>196</v>
+        <v>236</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>198</v>
+        <v>238</v>
       </c>
       <c r="J55" s="3">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>238</v>
+        <v>156</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>119</v>
+        <v>49</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F56" s="3"/>
       <c r="G56" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>240</v>
+        <v>87</v>
       </c>
       <c r="J56" s="3">
-        <v>23</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>49</v>
@@ -3840,54 +3869,54 @@
         <v>22</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>83</v>
+        <v>245</v>
       </c>
       <c r="J57" s="3">
-        <v>1</v>
+        <v>56</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>94</v>
+        <v>53</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>83</v>
+        <v>248</v>
       </c>
       <c r="J58" s="3">
-        <v>1</v>
+        <v>65</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>49</v>
@@ -3896,30 +3925,30 @@
         <v>42</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="J59" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>49</v>
@@ -3932,54 +3961,54 @@
         <v>22</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="J60" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>212</v>
+        <v>257</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>255</v>
+        <v>69</v>
       </c>
       <c r="J61" s="3">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>256</v>
+        <v>98</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>133</v>
+        <v>156</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>49</v>
@@ -3992,27 +4021,27 @@
         <v>22</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>69</v>
       </c>
       <c r="J62" s="3">
-        <v>68</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>260</v>
+        <v>175</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>133</v>
+        <v>176</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>49</v>
+        <v>123</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>42</v>
@@ -4022,84 +4051,86 @@
         <v>22</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="J63" s="3">
-        <v>21</v>
+        <v>64</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>215</v>
+        <v>137</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>148</v>
+        <v>49</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>144</v>
+        <v>267</v>
       </c>
       <c r="J64" s="3">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>266</v>
+        <v>66</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F65" s="3"/>
+        <v>42</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>113</v>
+      </c>
       <c r="G65" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>162</v>
+        <v>69</v>
       </c>
       <c r="J65" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>49</v>
@@ -4112,27 +4143,27 @@
         <v>22</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="J66" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>42</v>
@@ -4142,27 +4173,27 @@
         <v>22</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="J67" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>37</v>
@@ -4172,24 +4203,24 @@
         <v>22</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="J68" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>49</v>
@@ -4202,24 +4233,24 @@
         <v>22</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="J69" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>49</v>
@@ -4232,24 +4263,24 @@
         <v>22</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="J70" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>49</v>
@@ -4262,24 +4293,24 @@
         <v>22</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="J71" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>286</v>
+        <v>47</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>287</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>133</v>
+        <v>156</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>49</v>
@@ -4295,10 +4326,10 @@
         <v>288</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="J72" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -4309,13 +4340,13 @@
         <v>290</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
@@ -4325,10 +4356,10 @@
         <v>291</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>165</v>
+        <v>87</v>
       </c>
       <c r="J73" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -4339,13 +4370,13 @@
         <v>293</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
@@ -4355,7 +4386,7 @@
         <v>294</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>83</v>
+        <v>169</v>
       </c>
       <c r="J74" s="3">
         <v>1</v>
@@ -4366,10 +4397,10 @@
         <v>295</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>167</v>
+        <v>296</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>49</v>
@@ -4382,13 +4413,13 @@
         <v>22</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>297</v>
+        <v>87</v>
       </c>
       <c r="J75" s="3">
-        <v>27</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76">
@@ -4399,7 +4430,7 @@
         <v>299</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>49</v>
@@ -4415,21 +4446,21 @@
         <v>300</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>83</v>
+        <v>125</v>
       </c>
       <c r="J76" s="3">
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>192</v>
+        <v>137</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>49</v>
@@ -4442,27 +4473,27 @@
         <v>22</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>262</v>
+        <v>87</v>
       </c>
       <c r="J77" s="3">
-        <v>21</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>303</v>
+        <v>292</v>
       </c>
       <c r="B78" s="3" t="s">
         <v>304</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>305</v>
+        <v>193</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>119</v>
+        <v>49</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>37</v>
@@ -4472,70 +4503,70 @@
         <v>22</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>162</v>
+        <v>267</v>
       </c>
       <c r="J78" s="3">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>116</v>
+        <v>306</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>307</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>133</v>
+        <v>308</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>49</v>
+        <v>123</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>40</v>
+        <v>166</v>
       </c>
       <c r="J79" s="3">
-        <v>28</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>248</v>
+        <v>197</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>49</v>
+        <v>123</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>165</v>
+        <v>69</v>
       </c>
       <c r="J80" s="3">
         <v>0</v>
@@ -4543,109 +4574,111 @@
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>133</v>
+        <v>193</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F81" s="3"/>
+        <v>42</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>315</v>
+      </c>
       <c r="G81" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>315</v>
+        <v>69</v>
       </c>
       <c r="J81" s="3">
-        <v>88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>152</v>
+        <v>251</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>60</v>
+        <v>169</v>
       </c>
       <c r="J82" s="3">
-        <v>47</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>53</v>
+        <v>320</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>305</v>
+        <v>137</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>119</v>
+        <v>49</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="J83" s="3">
-        <v>44</v>
+        <v>89</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>322</v>
+        <v>301</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>324</v>
+        <v>156</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>119</v>
+        <v>49</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
@@ -4655,10 +4688,10 @@
         <v>325</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>175</v>
+        <v>69</v>
       </c>
       <c r="J84" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -4669,40 +4702,42 @@
         <v>327</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>248</v>
+        <v>197</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>49</v>
+        <v>123</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F85" s="3"/>
+      <c r="F85" s="3" t="s">
+        <v>328</v>
+      </c>
       <c r="G85" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>262</v>
+        <v>69</v>
       </c>
       <c r="J85" s="3">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>163</v>
+        <v>331</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>192</v>
+        <v>332</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>37</v>
@@ -4712,10 +4747,10 @@
         <v>22</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>165</v>
+        <v>69</v>
       </c>
       <c r="J86" s="3">
         <v>0</v>
@@ -4723,16 +4758,16 @@
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>331</v>
+        <v>206</v>
       </c>
       <c r="B87" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="C87" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="C87" s="3" t="s">
-        <v>196</v>
-      </c>
       <c r="D87" s="3" t="s">
-        <v>119</v>
+        <v>36</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>37</v>
@@ -4742,89 +4777,87 @@
         <v>22</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>172</v>
+        <v>69</v>
       </c>
       <c r="J87" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>196</v>
+        <v>156</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>119</v>
+        <v>49</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F88" s="3"/>
       <c r="G88" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>175</v>
+        <v>60</v>
       </c>
       <c r="J88" s="3">
-        <v>6</v>
+        <v>48</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>264</v>
+        <v>287</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>196</v>
+        <v>156</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>119</v>
+        <v>49</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>338</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="F89" s="3"/>
       <c r="G89" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>162</v>
+        <v>187</v>
       </c>
       <c r="J89" s="3">
-        <v>2</v>
+        <v>27</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>152</v>
+        <v>343</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>49</v>
+        <v>123</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>37</v>
@@ -4834,84 +4867,84 @@
         <v>22</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>175</v>
+        <v>110</v>
       </c>
       <c r="J90" s="3">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>264</v>
+        <v>346</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>196</v>
+        <v>347</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F91" s="3"/>
       <c r="G91" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>83</v>
+        <v>349</v>
       </c>
       <c r="J91" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>206</v>
+        <v>251</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>207</v>
+        <v>49</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F92" s="3"/>
       <c r="G92" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>172</v>
+        <v>267</v>
       </c>
       <c r="J92" s="3">
-        <v>4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>349</v>
+        <v>167</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>152</v>
+        <v>193</v>
       </c>
       <c r="D93" s="3" t="s">
         <v>49</v>
@@ -4924,10 +4957,10 @@
         <v>22</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>83</v>
+        <v>169</v>
       </c>
       <c r="J93" s="3">
         <v>1</v>
@@ -4935,16 +4968,16 @@
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>152</v>
+        <v>197</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>49</v>
+        <v>123</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>37</v>
@@ -4954,94 +4987,94 @@
         <v>22</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="J94" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>355</v>
+        <v>311</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F95" s="3"/>
+      <c r="F95" s="3" t="s">
+        <v>359</v>
+      </c>
       <c r="G95" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="J95" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>358</v>
+        <v>173</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>359</v>
+        <v>156</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>148</v>
+        <v>49</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F96" s="3"/>
       <c r="G96" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="J96" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>362</v>
+        <v>327</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>363</v>
+        <v>197</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F97" s="3" t="s">
-        <v>338</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="F97" s="3"/>
       <c r="G97" s="3" t="s">
         <v>22</v>
       </c>
@@ -5049,14 +5082,76 @@
         <v>364</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>83</v>
+        <v>166</v>
       </c>
       <c r="J97" s="3">
-        <v>1</v>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F98" s="3"/>
+      <c r="G98" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H98" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="I98" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="J98" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F99" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="G99" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H99" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="I99" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="J99" s="3">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J97"/>
+  <autoFilter ref="A1:J99"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5154,6 +5249,8 @@
     <hyperlink ref="H95" r:id="rId94"/>
     <hyperlink ref="H96" r:id="rId95"/>
     <hyperlink ref="H97" r:id="rId96"/>
+    <hyperlink ref="H98" r:id="rId97"/>
+    <hyperlink ref="H99" r:id="rId98"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5161,9 +5258,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="35" customWidth="1"/>
-    <col min="2" max="2" width="45" customWidth="1"/>
-    <col min="3" max="3" width="44" customWidth="1"/>
+    <col min="1" max="1" width="56" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
@@ -5195,32 +5292,32 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>163</v>
+        <v>62</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>152</v>
+        <v>49</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>164</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>205</v>
+        <v>47</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>206</v>
+        <v>156</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -5228,18 +5325,18 @@
         <v>22</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>208</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -5247,18 +5344,18 @@
         <v>22</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>47</v>
+        <v>256</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>225</v>
+        <v>257</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5266,18 +5363,18 @@
         <v>22</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>226</v>
+        <v>258</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>231</v>
+        <v>98</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>232</v>
+        <v>259</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -5285,18 +5382,18 @@
         <v>22</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>233</v>
+        <v>260</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>246</v>
+        <v>66</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>247</v>
+        <v>268</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>248</v>
+        <v>137</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -5304,18 +5401,18 @@
         <v>22</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>250</v>
+        <v>269</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>289</v>
+        <v>47</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>133</v>
+        <v>156</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -5323,18 +5420,18 @@
         <v>22</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>248</v>
+        <v>197</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -5342,18 +5439,18 @@
         <v>22</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>329</v>
+        <v>313</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>163</v>
+        <v>314</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -5361,11 +5458,87 @@
         <v>22</v>
       </c>
       <c r="G10" s="3" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="s">
         <v>330</v>
       </c>
+      <c r="B13" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>335</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G10"/>
+  <autoFilter ref="A1:G14"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -5376,6 +5549,10 @@
     <hyperlink ref="G8" r:id="rId7"/>
     <hyperlink ref="G9" r:id="rId8"/>
     <hyperlink ref="G10" r:id="rId9"/>
+    <hyperlink ref="G11" r:id="rId10"/>
+    <hyperlink ref="G12" r:id="rId11"/>
+    <hyperlink ref="G13" r:id="rId12"/>
+    <hyperlink ref="G14" r:id="rId13"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5389,15 +5566,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>367</v>
+        <v>315</v>
       </c>
       <c r="B2" s="3">
         <v>15</v>
@@ -5405,15 +5582,15 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="B3" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="B4" s="3">
         <v>14</v>
@@ -5421,7 +5598,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B5" s="3">
         <v>14</v>
@@ -5429,7 +5606,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>370</v>
+        <v>113</v>
       </c>
       <c r="B6" s="3">
         <v>9</v>
@@ -5437,23 +5614,23 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>371</v>
+        <v>328</v>
       </c>
       <c r="B7" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="B8" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="B9" s="3">
         <v>8</v>
@@ -5461,7 +5638,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>338</v>
+        <v>379</v>
       </c>
       <c r="B10" s="3">
         <v>8</v>
@@ -5469,15 +5646,15 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>109</v>
+        <v>359</v>
       </c>
       <c r="B11" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="B12" s="3">
         <v>7</v>
@@ -5485,7 +5662,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="B13" s="3">
         <v>6</v>
@@ -5493,7 +5670,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="B14" s="3">
         <v>6</v>
@@ -5501,7 +5678,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="B15" s="3">
         <v>6</v>
@@ -5509,7 +5686,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B16" s="3">
         <v>5</v>
@@ -5531,20 +5708,20 @@
         <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="B2" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="B3" s="3">
         <v>3</v>
@@ -5552,7 +5729,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B4" s="3">
         <v>3</v>
@@ -5560,7 +5737,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -5568,7 +5745,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -5576,7 +5753,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="B7" s="3">
         <v>3</v>
@@ -5584,7 +5761,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B8" s="3">
         <v>3</v>
@@ -5592,15 +5769,15 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>264</v>
+        <v>48</v>
       </c>
       <c r="B9" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>48</v>
+        <v>112</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -5608,7 +5785,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>108</v>
+        <v>171</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5616,7 +5793,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5624,7 +5801,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5632,7 +5809,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>212</v>
+        <v>287</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -5640,18 +5817,18 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>56</v>
+        <v>311</v>
       </c>
       <c r="B15" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>102</v>
+        <v>327</v>
       </c>
       <c r="B16" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5669,16 +5846,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
     </row>
     <row r="2">
@@ -5686,7 +5863,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C2" s="3">
         <v>13.4</v>
@@ -5700,13 +5877,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
       <c r="C3" s="3">
-        <v>9.2</v>
+        <v>12.0</v>
       </c>
       <c r="D3" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -5714,10 +5891,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>62</v>
+        <v>93</v>
       </c>
       <c r="C4" s="3">
-        <v>7.6</v>
+        <v>9.2</v>
       </c>
       <c r="D4" s="3">
         <v>3</v>
@@ -5756,7 +5933,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="C7" s="3">
         <v>4.2</v>
@@ -5770,13 +5947,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>179</v>
+        <v>112</v>
       </c>
       <c r="C8" s="3">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="D8" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -5784,10 +5961,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>264</v>
+        <v>167</v>
       </c>
       <c r="C9" s="3">
-        <v>4.0</v>
+        <v>3.6</v>
       </c>
       <c r="D9" s="3">
         <v>3</v>
@@ -5798,13 +5975,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>108</v>
+        <v>175</v>
       </c>
       <c r="C10" s="3">
         <v>3.6</v>
       </c>
       <c r="D10" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -5812,13 +5989,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>163</v>
+        <v>56</v>
       </c>
       <c r="C11" s="3">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="D11" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -5826,13 +6003,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>56</v>
+        <v>171</v>
       </c>
       <c r="C12" s="3">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="D12" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -5840,13 +6017,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>123</v>
+        <v>173</v>
       </c>
       <c r="C13" s="3">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="D13" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -5854,10 +6031,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>169</v>
+        <v>311</v>
       </c>
       <c r="C14" s="3">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="D14" s="3">
         <v>2</v>
@@ -5868,10 +6045,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>195</v>
+        <v>327</v>
       </c>
       <c r="C15" s="3">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="D15" s="3">
         <v>2</v>
@@ -5882,13 +6059,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>212</v>
+        <v>127</v>
       </c>
       <c r="C16" s="3">
         <v>2.4</v>
       </c>
       <c r="D16" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -5908,21 +6085,21 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B2" s="3">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
     </row>
     <row r="3">
@@ -5930,10 +6107,10 @@
         <v>37</v>
       </c>
       <c r="B3" s="3">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
     </row>
     <row r="4">
@@ -5941,10 +6118,10 @@
         <v>42</v>
       </c>
       <c r="B4" s="3">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
     </row>
   </sheetData>
@@ -5963,7 +6140,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
     </row>
     <row r="2">
@@ -5971,20 +6148,20 @@
         <v>49</v>
       </c>
       <c r="B2" s="3">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B3" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>148</v>
+        <v>36</v>
       </c>
       <c r="B4" s="3">
         <v>5</v>
@@ -5992,7 +6169,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>36</v>
+        <v>152</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -6000,15 +6177,15 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>207</v>
+        <v>107</v>
       </c>
       <c r="B6" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>103</v>
+        <v>162</v>
       </c>
       <c r="B7" s="3">
         <v>1</v>
@@ -6016,7 +6193,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>158</v>
+        <v>204</v>
       </c>
       <c r="B8" s="3">
         <v>1</v>
@@ -6024,7 +6201,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="B9" s="3">
         <v>1</v>
@@ -6051,10 +6228,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>25</v>
@@ -6066,10 +6243,10 @@
         <v>27</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>20</v>
@@ -6086,7 +6263,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>56</v>
@@ -6095,22 +6272,22 @@
         <v>57</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>255</v>
+        <v>401</v>
       </c>
     </row>
     <row r="3">
@@ -6118,31 +6295,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
     </row>
     <row r="4">
@@ -6150,13 +6327,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>404</v>
+        <v>137</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>405</v>
@@ -6165,16 +6342,16 @@
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5">
@@ -6182,31 +6359,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>133</v>
+        <v>415</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="F5" s="3">
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>69</v>
+        <v>148</v>
       </c>
     </row>
     <row r="6">
@@ -6214,31 +6391,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>412</v>
+        <v>358</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>413</v>
+        <v>324</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="F6" s="3">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>144</v>
+        <v>421</v>
       </c>
     </row>
     <row r="7">
@@ -6246,31 +6423,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>337</v>
+        <v>422</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>398</v>
+        <v>425</v>
       </c>
       <c r="F7" s="3">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
     </row>
     <row r="8">
@@ -6278,31 +6455,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>424</v>
+        <v>207</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>425</v>
+        <v>405</v>
       </c>
       <c r="F8" s="3">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>428</v>
+        <v>401</v>
       </c>
     </row>
     <row r="9">
@@ -6310,31 +6487,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>430</v>
+        <v>175</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>206</v>
+        <v>176</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="F9" s="3">
         <v>84</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>255</v>
+        <v>436</v>
       </c>
     </row>
     <row r="10">
@@ -6342,31 +6519,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>169</v>
+        <v>438</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>170</v>
+        <v>193</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>398</v>
+        <v>439</v>
       </c>
       <c r="F10" s="3">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>297</v>
+        <v>97</v>
       </c>
     </row>
     <row r="11">
@@ -6374,31 +6551,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>192</v>
+        <v>137</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>405</v>
       </c>
       <c r="F11" s="3">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>93</v>
+        <v>446</v>
       </c>
     </row>
     <row r="12">
@@ -6406,31 +6583,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>133</v>
+        <v>449</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>398</v>
       </c>
       <c r="F12" s="3">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>444</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13">
@@ -6438,31 +6615,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>405</v>
+        <v>439</v>
       </c>
       <c r="F13" s="3">
         <v>74</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>297</v>
+        <v>436</v>
       </c>
     </row>
     <row r="14">
@@ -6470,31 +6647,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>215</v>
+        <v>332</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>405</v>
+        <v>439</v>
       </c>
       <c r="F14" s="3">
         <v>70</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>69</v>
+        <v>125</v>
       </c>
     </row>
     <row r="15">
@@ -6502,31 +6679,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>403</v>
+        <v>460</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>404</v>
+        <v>461</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>405</v>
       </c>
       <c r="F15" s="3">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>453</v>
+        <v>462</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>454</v>
+        <v>463</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>121</v>
+        <v>464</v>
       </c>
     </row>
     <row r="16">
@@ -6534,31 +6711,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>455</v>
+        <v>465</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>456</v>
+        <v>466</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>457</v>
+        <v>137</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>398</v>
       </c>
       <c r="F16" s="3">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>459</v>
+        <v>468</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>460</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6566,31 +6743,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>214</v>
+        <v>470</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>196</v>
+        <v>367</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>398</v>
+        <v>425</v>
       </c>
       <c r="F17" s="3">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>462</v>
+        <v>471</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>464</v>
+        <v>169</v>
       </c>
     </row>
     <row r="18">
@@ -6598,31 +6775,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>466</v>
+        <v>356</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>133</v>
+        <v>197</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>392</v>
+        <v>405</v>
       </c>
       <c r="F18" s="3">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>65</v>
+        <v>87</v>
       </c>
     </row>
     <row r="19">
@@ -6630,31 +6807,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>332</v>
+        <v>477</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>196</v>
+        <v>478</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="F19" s="3">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>470</v>
+        <v>479</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>471</v>
+        <v>480</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>83</v>
+        <v>178</v>
       </c>
     </row>
     <row r="20">
@@ -6662,31 +6839,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>472</v>
+        <v>481</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>473</v>
+        <v>482</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>474</v>
+        <v>156</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="F20" s="3">
         <v>48</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>476</v>
+        <v>484</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>172</v>
+        <v>87</v>
       </c>
     </row>
     <row r="21">
@@ -6694,31 +6871,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>267</v>
+        <v>486</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>152</v>
+        <v>197</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>398</v>
+        <v>425</v>
       </c>
       <c r="F21" s="3">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>478</v>
+        <v>487</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>479</v>
+        <v>488</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>83</v>
+        <v>154</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W44.xlsx
+++ b/reports/devops-jobs-israel-2026-W44.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="507">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="496">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-28T12:39:34</t>
+    <t xml:space="preserve">2026-10-29T12:48:33</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -297,1152 +297,1125 @@
     <t xml:space="preserve">2026-09-14</t>
   </si>
   <si>
-    <t xml:space="preserve">Agent Platform Engineer</t>
+    <t xml:space="preserve">DevOps Engineer</t>
   </si>
   <si>
     <t xml:space="preserve">Similarweb</t>
   </si>
   <si>
-    <t xml:space="preserve">Tel Aviv-Yafo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/8264120</t>
+    <t xml:space="preserve">AWS, GCP, Docker, Linux, Python, Networking, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7938197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Backend Engineer, Platform Foundations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Ansible, Docker, CI/CD, Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7962665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Terraform, CI/CD, Linux, Python, Bash/Shell, Networking, Security, Argo CD, Observability, Tracing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8695882002?gh_jid=8695882002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior IT Infrastructure Operations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Terraform, Docker, CI/CD, Python, Networking, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8882905002?gh_jid=8882905002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Director of Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yotpo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.yotpo.com/careers/gid-8143530?gh_jid=8143530</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staff Engineer - Office of the CTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.yotpo.com/careers/gid-8211515?gh_jid=8211515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riskified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lisbon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel (other)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8873995002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Lead (FedRAMP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orcasecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">United States</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, CI/CD, Helm, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://orca.security/about/careers/6149333004?gh_jid=6149333004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aidoc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-aidoc-4465646027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentee Robotics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-mentee-robotics-4481407411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Platform Engineer- CTI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dream</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-platform-engineer-cti-at-dream-4465727084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Priority Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-priority-software-4477000056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harmonic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-harmonic-4360460066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deloitte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-deloitte-4479294849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pango</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-devops-engineer-at-pango-4481441009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Point Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-check-point-software-4483375334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-comblack-4483574435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Principal DevOps Engineer (Cortex Cloud)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-devops-engineer-cortex-cloud-at-palo-alto-networks-4443693726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logica-IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-logica-it-4482293600</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-4481638138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BigID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-bigid-4482680687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer - Cloud Infra Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-infra-team-at-wix-4480881694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CommBox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-commbox-4484931014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer - Data Platform (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-data-platform-cortex-at-palo-alto-networks-4455871961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer- Detection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-detection-at-dream-4484937206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Devops Engineer - AI Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bridgewise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-ai-team-at-bridgewise-4482680803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform DevOps Engineer - Core Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jeen.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-devops-engineer-core-platform-at-jeen-ai-4482092082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checkmarx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-checkmarx-4439196775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IRONSCALES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-ironscales-4483869791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Speedata.io</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-speedata-io-4483379335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-engineer-at-comblack-4483582140</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zenity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-zenity-4478465745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4474645372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4481079700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SR DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bitsight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-bitsight-4483570331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personetics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-personetics-4428829912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeValue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-codevalue-4483726365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elementor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-elementor-4482868447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-sqlink-group-4482292829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Webiks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-reliability-engineer-at-webiks-4483579517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Founding DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stealth-Mode Cybersecurity Startup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/founding-devops-at-stealth-mode-cybersecurity-startup-4482932513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Data Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-data-infrastructure-engineer-at-evoke-4462157157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE / DevOps Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">april</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-devops-lead-at-april-4416179005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SciPlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-sciplay-4391151881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevSecOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PayPlus - The Future of Payments &amp; Commerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devsecops-engineer-at-payplus-the-future-of-payments-commerce-4482999139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineering - Storage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineering-storage-at-nvidia-4457190574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/observability-platform-team-lead-at-gong-4484452499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure Engineer - Core Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-core-systems-at-wix-4483368404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infra Engineer Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infra-engineer-team-lead-at-dialog-4481085538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software System Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-system-reliability-engineer-at-cisco-4483388333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oriient</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-oriient-4484447442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Software Engineer -Platform Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viz.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-software-engineer-platform-team-at-viz-ai-4437383686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sunbit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-sunbit-4484439423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Data Infrastructure Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-data-infrastructure-team-leader-at-evoke-4484943062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Platform Engineer (Infra Platform)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">monday.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-infra-platform-at-monday-com-4483388052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI &amp; Software Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BioCatch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-software-infra-engineer-at-biocatch-4484927514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ScaleOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-scaleops-4483763089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior GPU Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zesty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-gpu-platform-engineer-at-zesty-4481405125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior AI &amp; Software Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-software-infra-engineer-at-biocatch-4447894244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claroty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-claroty-4482292784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Millennium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-millennium-4482698329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-alice-formerly-activefence-4472729462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Platform Engineer (Mid-level)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobgether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-mid-level-at-jobgether-4481691238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OpenShift Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential Careers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/openshift-platform-engineer-at-confidential-careers-4482299668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Agentic AI Engineer (AWS/DevOps)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Directeam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-agentic-ai-engineer-aws-devops-at-directeam-4482501198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal Data Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MediaForce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-data-platform-engineer-at-mediaforce-4481460917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calanit by one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-calanit-by-one-4484447830</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Infrastructure &amp; Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moon Active</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-cloud-engineer-at-moon-active-4447031167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure Infrastructure Engineer – AI &amp; Automation (5524)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INGIMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/azure-infrastructure-engineer-%E2%80%93-ai-automation-5524-at-ingima-4484427543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT DevOps Engineer - 244284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-devops-engineer-244284-at-experis-israel-4482290223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integress, Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-engineer-at-integress-inc-4483842402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prisma Photonics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-prisma-photonics-4432235322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-engineer-at-cato-networks-4463471007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal Devops &amp; Infra Tech Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-infra-tech-lead-at-sunbit-4474134295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Integration &amp; Infrastructure Engineer (Advanced storage infrastructure for AI workloads)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sandisk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-integration-infrastructure-engineer-advanced-storage-infrastructure-for-ai-workloads-at-sandisk-4478351208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moveo Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-infrastructure-engineer-at-moveo-source-4480775799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-elbit-systems-israel-4474036853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OpenShift Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/openshift-infrastructure-engineer-at-comblack-4484951649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-infrastructure-engineer-at-logica-it-4481435276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E2E Solutions IL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-e2e-solutions-il-4482928669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JobsSeek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Midreshet Ben-Gurion, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-linux-system-administrator-at-jobsseek-4483393914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developer Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=8264438&amp;gh_jid=8264438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Development Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clarivate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/development-operations-engineer-at-clarivate-4467992253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rapyd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux &amp; HPC Systems Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Novocure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tirat HaCarmel, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-hpc-systems-engineer-at-novocure-4478872342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System &amp; Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-infrastructure-engineer-at-final-4475581791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cross River</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-at-cross-river-4478788112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HPC Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4471977303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Monitoring Engineer (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-monitoring-engineer-student-position-at-upwind-security-4476759903</t>
   </si>
   <si>
     <t xml:space="preserve">2026-10-08</t>
   </si>
   <si>
-    <t xml:space="preserve">DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, GCP, Docker, Linux, Python, Networking, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7938197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Backend Engineer, Platform Foundations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Ansible, Docker, CI/CD, Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7962665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior IT Infrastructure Operations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Terraform, Docker, CI/CD, Python, Networking, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8882905002?gh_jid=8882905002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Director of Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yotpo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.yotpo.com/careers/gid-8143530?gh_jid=8143530</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staff Engineer - Office of the CTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.yotpo.com/careers/gid-8211515?gh_jid=8211515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior AI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riskified</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lisbon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel (other)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8873995002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Lead (FedRAMP)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Orcasecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">United States</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, CI/CD, Helm, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://orca.security/about/careers/6149333004?gh_jid=6149333004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aidoc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-aidoc-4465646027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentee Robotics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-mentee-robotics-4481407411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Platform Engineer- CTI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dream</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-platform-engineer-cti-at-dream-4465727084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Priority Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-priority-software-4477000056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harmonic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-harmonic-4360460066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deloitte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-deloitte-4479294849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pango</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-devops-engineer-at-pango-4481441009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check Point Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-check-point-software-4483375334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-comblack-4483574435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Principal DevOps Engineer (Cortex Cloud)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-devops-engineer-cortex-cloud-at-palo-alto-networks-4443693726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logica-IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-logica-it-4482293600</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-4481638138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BigID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-bigid-4482680687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer - Cloud Infra Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-infra-team-at-wix-4480881694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer, AIOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-aiops-at-nvidia-4471970512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer and SRE Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upstream Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-and-sre-lead-at-upstream-security-4482467626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Devops Engineer - AI Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bridgewise</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-ai-team-at-bridgewise-4482680803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform DevOps Engineer - Core Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jeen.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-devops-engineer-core-platform-at-jeen-ai-4482092082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experienced DevOps Engineer (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/experienced-devops-engineer-cortex-at-palo-alto-networks-4462513797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Speedata.io</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-speedata-io-4483379335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-engineer-at-comblack-4483582140</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zenity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-zenity-4478465745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4481079700</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SR DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bitsight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-bitsight-4483570331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Personetics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-personetics-4428829912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeValue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-codevalue-4483726365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elementor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-elementor-4482868447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pontera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-pontera-4481315450</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-sqlink-group-4482292829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Webiks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-reliability-engineer-at-webiks-4483579517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-devops-engineer-at-jeen-ai-4482082697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Software Engineer, DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aiven</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-software-engineer-devops-at-aiven-4426867332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Founding DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stealth-Mode Cybersecurity Startup</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/founding-devops-at-stealth-mode-cybersecurity-startup-4482932513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Data Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-data-infrastructure-engineer-at-evoke-4462157157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SciPlay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-sciplay-4391151881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevSecOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PayPlus - The Future of Payments &amp; Commerce</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devsecops-engineer-at-payplus-the-future-of-payments-commerce-4482999139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Tech Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-wix-4483537365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claroty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-claroty-4482292784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oriient</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-oriient-4484447442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineering - Storage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineering-storage-at-nvidia-4457190574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. SRE AI Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-sre-ai-engineer-at-navan-4437742346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/observability-platform-team-lead-at-gong-4484452499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure Engineer - Core Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-core-systems-at-wix-4483368404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infra Engineer Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dialog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infra-engineer-team-lead-at-dialog-4481085538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software System Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-system-reliability-engineer-at-cisco-4483388333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Backend Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akamai Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-backend-infrastructure-engineer-at-akamai-technologies-4473769865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Software Engineer -Platform Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viz.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-software-engineer-platform-team-at-viz-ai-4437383686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Immunai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-immunai-4482405033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sunbit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-sunbit-4484439423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Platform Engineer (Infra Platform)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monday.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-infra-platform-at-monday-com-4483388052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ScaleOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-scaleops-4483763089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior GPU Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zesty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-gpu-platform-engineer-at-zesty-4481405125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI &amp; Software Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BioCatch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-software-infra-engineer-at-biocatch-4447894244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Millennium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-millennium-4482698329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-alice-formerly-activefence-4472729462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Platform Engineer (Mid-level)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobgether</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-mid-level-at-jobgether-4481691238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OpenShift Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential Careers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/openshift-platform-engineer-at-confidential-careers-4482299668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Agentic AI Engineer (AWS/DevOps)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Directeam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-agentic-ai-engineer-aws-devops-at-directeam-4482501198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principal Data Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MediaForce</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-data-platform-engineer-at-mediaforce-4481460917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Infrastructure &amp; Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moon Active</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-cloud-engineer-at-moon-active-4447031167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calanit by one</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-calanit-by-one-4484447830</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure Infrastructure Engineer – AI &amp; Automation (5524)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INGIMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/azure-infrastructure-engineer-%E2%80%93-ai-automation-5524-at-ingima-4484427543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT DevOps Engineer - 244284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-devops-engineer-244284-at-experis-israel-4482290223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Integress, Inc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-engineer-at-integress-inc-4483842402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-engineer-at-cato-networks-4463471007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principal Devops &amp; Infra Tech Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-infra-tech-lead-at-sunbit-4474134295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Integration &amp; Infrastructure Engineer (Advanced storage infrastructure for AI workloads)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sandisk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-integration-infrastructure-engineer-advanced-storage-infrastructure-for-ai-workloads-at-sandisk-4478351208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moveo Source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-infrastructure-engineer-at-moveo-source-4480775799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-elbit-systems-israel-4474036853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OpenShift Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/openshift-infrastructure-engineer-at-comblack-4483564559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer (37823)</t>
+    <t xml:space="preserve">Junior Technical Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New York City</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, GCP, Cloud (any), Git, Terraform/IaC, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/melio/jobs/7995568003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security Analyst (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/security-analyst-student-position-at-upwind-security-4473525994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Integration Student, SPIV team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annapurna Labs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-integration-student-spiv-team-at-annapurna-labs-4456348779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student Software Engineer – Cloud, Big Data, Billing &amp; AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Cloud (any), Docker, Kubernetes, CI/CD, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-software-engineer-%E2%80%93-cloud-big-data-billing-ai-at-sap-4476596020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kela Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior CAD Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cad-engineer-university-graduate-google-cloud-at-google-4483213993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator (37866)</t>
   </si>
   <si>
     <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-37823-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4482463663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-confidential-careers-4481088252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-infrastructure-engineer-at-logica-it-4481435276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft System Administrator (5515)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-administrator-5515-at-ingima-4483376293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E2E Solutions IL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-e2e-solutions-il-4482928669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JobsSeek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Midreshet Ben-Gurion, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-linux-system-administrator-at-jobsseek-4483393914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developer Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=8264438&amp;gh_jid=8264438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Development Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clarivate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/development-operations-engineer-at-clarivate-4467992253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rapyd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux &amp; HPC Systems Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Novocure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tirat HaCarmel, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-hpc-systems-engineer-at-novocure-4478872342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-calanit-by-one-4478305717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System &amp; Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-infrastructure-engineer-at-final-4475581791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cross River</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-at-cross-river-4478788112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HPC Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4471977303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Monitoring Engineer (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upwind Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-monitoring-engineer-student-position-at-upwind-security-4476759903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Technical Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New York City</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, GCP, Cloud (any), Git, Terraform/IaC, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/melio/jobs/7995568003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security Analyst (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/security-analyst-student-position-at-upwind-security-4473525994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student Software Engineer – Cloud, Big Data, Billing &amp; AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Cloud (any), Docker, Kubernetes, CI/CD, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-software-engineer-%E2%80%93-cloud-big-data-billing-ai-at-sap-4476596020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kela Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior CAD Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cad-engineer-university-graduate-google-cloud-at-google-4483213993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator (37866)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
   </si>
   <si>
@@ -1464,18 +1437,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-tier-3-%E2%80%93-it-infrastructure-cybersecurity-at-mornex-4474264582</t>
   </si>
   <si>
-    <t xml:space="preserve">Network Operations Center</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compie Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Monitoring, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-operations-center-at-compie-technologies-4483540095</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
   </si>
   <si>
@@ -1488,6 +1449,15 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
   </si>
   <si>
+    <t xml:space="preserve">NOC Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Kubernetes, Networking, Monitoring, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-technician-at-confidential-careers-4482513067</t>
+  </si>
+  <si>
     <t xml:space="preserve">Junior SysAdmin / Linux</t>
   </si>
   <si>
@@ -1503,13 +1473,10 @@
     <t xml:space="preserve">Cloud (any)</t>
   </si>
   <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Virtualization</t>
   </si>
   <si>
     <t xml:space="preserve">Terraform/IaC</t>
@@ -1664,7 +1631,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7">
@@ -1672,7 +1639,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -1680,7 +1647,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9">
@@ -1688,7 +1655,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>844</v>
+        <v>834</v>
       </c>
     </row>
     <row r="10">
@@ -1760,7 +1727,7 @@
         <v>22</v>
       </c>
       <c r="B19" s="3">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="20">
@@ -1787,28 +1754,28 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>405</v>
+        <v>393</v>
       </c>
       <c r="B2" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>398</v>
+        <v>387</v>
       </c>
       <c r="B3" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>439</v>
+        <v>423</v>
       </c>
       <c r="B4" s="3">
         <v>6</v>
@@ -1816,7 +1783,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>425</v>
+        <v>409</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -1824,7 +1791,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>489</v>
+        <v>479</v>
       </c>
       <c r="B6" s="3">
         <v>2</v>
@@ -1843,47 +1810,47 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>373</v>
+        <v>362</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>490</v>
+        <v>480</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>491</v>
+        <v>481</v>
       </c>
       <c r="B2" s="3">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>359</v>
+        <v>482</v>
       </c>
       <c r="B3" s="3">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>492</v>
+        <v>360</v>
       </c>
       <c r="B4" s="3">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>493</v>
+        <v>370</v>
       </c>
       <c r="B5" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>382</v>
+        <v>483</v>
       </c>
       <c r="B6" s="3">
         <v>23</v>
@@ -1891,7 +1858,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="B7" s="3">
         <v>20</v>
@@ -1899,15 +1866,15 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>494</v>
+        <v>484</v>
       </c>
       <c r="B8" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>495</v>
+        <v>485</v>
       </c>
       <c r="B9" s="3">
         <v>17</v>
@@ -1915,23 +1882,23 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>379</v>
+        <v>309</v>
       </c>
       <c r="B10" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>376</v>
+        <v>322</v>
       </c>
       <c r="B11" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>328</v>
+        <v>368</v>
       </c>
       <c r="B12" s="3">
         <v>10</v>
@@ -1939,34 +1906,34 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>315</v>
+        <v>365</v>
       </c>
       <c r="B13" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>375</v>
+        <v>364</v>
       </c>
       <c r="B14" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>496</v>
+        <v>486</v>
       </c>
       <c r="B15" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>497</v>
+        <v>367</v>
       </c>
       <c r="B16" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -1991,13 +1958,13 @@
         <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>498</v>
+        <v>487</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>499</v>
+        <v>488</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>500</v>
+        <v>489</v>
       </c>
     </row>
     <row r="2">
@@ -2008,10 +1975,10 @@
         <v>22</v>
       </c>
       <c r="C2" s="3">
-        <v>12.1</v>
+        <v>11.8</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>501</v>
+        <v>490</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -2020,88 +1987,88 @@
         <v>22</v>
       </c>
       <c r="B3" s="3">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C3" s="3">
-        <v>36.9</v>
+        <v>37.1</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>501</v>
+        <v>490</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>502</v>
+        <v>491</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>7.9</v>
+        <v>9.2</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>501</v>
+        <v>490</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>503</v>
+        <v>492</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>501</v>
+        <v>490</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>504</v>
+        <v>493</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>32.2</v>
+        <v>28.7</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>501</v>
+        <v>490</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>505</v>
+        <v>494</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>18.5</v>
+        <v>13.6</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>501</v>
+        <v>490</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>506</v>
+        <v>495</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>29.9</v>
+        <v>30.9</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>501</v>
+        <v>490</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2185,7 +2152,7 @@
         <v>40</v>
       </c>
       <c r="J2" s="3">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
@@ -2217,7 +2184,7 @@
         <v>40</v>
       </c>
       <c r="J3" s="3">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
@@ -2249,7 +2216,7 @@
         <v>46</v>
       </c>
       <c r="J4" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -2281,7 +2248,7 @@
         <v>52</v>
       </c>
       <c r="J5" s="3">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6">
@@ -2313,7 +2280,7 @@
         <v>52</v>
       </c>
       <c r="J6" s="3">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7">
@@ -2345,7 +2312,7 @@
         <v>60</v>
       </c>
       <c r="J7" s="3">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8">
@@ -2377,7 +2344,7 @@
         <v>65</v>
       </c>
       <c r="J8" s="3">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9">
@@ -2409,7 +2376,7 @@
         <v>69</v>
       </c>
       <c r="J9" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -2441,7 +2408,7 @@
         <v>73</v>
       </c>
       <c r="J10" s="3">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11">
@@ -2473,7 +2440,7 @@
         <v>77</v>
       </c>
       <c r="J11" s="3">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12">
@@ -2505,7 +2472,7 @@
         <v>83</v>
       </c>
       <c r="J12" s="3">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13">
@@ -2537,7 +2504,7 @@
         <v>87</v>
       </c>
       <c r="J13" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -2569,7 +2536,7 @@
         <v>91</v>
       </c>
       <c r="J14" s="3">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15">
@@ -2580,7 +2547,7 @@
         <v>93</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>94</v>
+        <v>49</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>49</v>
@@ -2589,68 +2556,68 @@
         <v>37</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H15" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="I15" s="3" t="s">
-        <v>97</v>
-      </c>
       <c r="J15" s="3">
-        <v>20</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>93</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="J16" s="3">
-        <v>72</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>80</v>
-      </c>
       <c r="D17" s="3" t="s">
-        <v>49</v>
+        <v>102</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>103</v>
@@ -2662,50 +2629,50 @@
         <v>104</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="J17" s="3">
-        <v>62</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>42</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H18" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>110</v>
-      </c>
       <c r="J18" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>111</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>112</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>49</v>
@@ -2717,27 +2684,27 @@
         <v>37</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H19" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="I19" s="3" t="s">
-        <v>115</v>
-      </c>
       <c r="J19" s="3">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>49</v>
@@ -2749,33 +2716,33 @@
         <v>42</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H20" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>119</v>
-      </c>
       <c r="J20" s="3">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="C21" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="D21" s="3" t="s">
         <v>122</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>123</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>42</v>
@@ -2785,24 +2752,24 @@
         <v>23</v>
       </c>
       <c r="H21" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="I21" s="3" t="s">
-        <v>125</v>
-      </c>
       <c r="J21" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="C22" s="3" t="s">
         <v>127</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>128</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>49</v>
@@ -2811,51 +2778,51 @@
         <v>42</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>52</v>
       </c>
       <c r="J22" s="3">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="C23" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>133</v>
-      </c>
       <c r="D23" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>42</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J23" s="3">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="24">
@@ -2863,10 +2830,10 @@
         <v>47</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>136</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>137</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>49</v>
@@ -2879,24 +2846,24 @@
         <v>22</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>60</v>
       </c>
       <c r="J24" s="3">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>139</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>140</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>49</v>
@@ -2909,24 +2876,24 @@
         <v>22</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>87</v>
       </c>
       <c r="J25" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>143</v>
-      </c>
       <c r="C26" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>49</v>
@@ -2939,13 +2906,13 @@
         <v>22</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>91</v>
       </c>
       <c r="J26" s="3">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="27">
@@ -2953,13 +2920,13 @@
         <v>47</v>
       </c>
       <c r="B27" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="C27" s="3" t="s">
-        <v>146</v>
-      </c>
       <c r="D27" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>42</v>
@@ -2969,27 +2936,27 @@
         <v>22</v>
       </c>
       <c r="H27" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="I27" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="I27" s="3" t="s">
-        <v>148</v>
-      </c>
       <c r="J27" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="B28" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="C28" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="D28" s="3" t="s">
         <v>151</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>152</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>42</v>
@@ -2999,24 +2966,24 @@
         <v>22</v>
       </c>
       <c r="H28" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="I28" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="I28" s="3" t="s">
-        <v>154</v>
-      </c>
       <c r="J28" s="3">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="B29" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>155</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>156</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>49</v>
@@ -3029,27 +2996,27 @@
         <v>22</v>
       </c>
       <c r="H29" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="I29" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="I29" s="3" t="s">
-        <v>158</v>
-      </c>
       <c r="J29" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B30" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="C30" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="D30" s="3" t="s">
         <v>161</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>162</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>37</v>
@@ -3059,24 +3026,24 @@
         <v>22</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I30" s="3" t="s">
         <v>87</v>
       </c>
       <c r="J30" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>49</v>
@@ -3089,24 +3056,24 @@
         <v>22</v>
       </c>
       <c r="H31" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="I31" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="I31" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="J31" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>49</v>
@@ -3119,24 +3086,24 @@
         <v>22</v>
       </c>
       <c r="H32" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="I32" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>169</v>
-      </c>
       <c r="J32" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>171</v>
-      </c>
       <c r="C33" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>49</v>
@@ -3149,13 +3116,13 @@
         <v>22</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>73</v>
       </c>
       <c r="J33" s="3">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="34">
@@ -3163,10 +3130,10 @@
         <v>47</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>49</v>
@@ -3179,13 +3146,13 @@
         <v>22</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I34" s="3" t="s">
         <v>69</v>
       </c>
       <c r="J34" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -3193,13 +3160,13 @@
         <v>47</v>
       </c>
       <c r="B35" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C35" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="C35" s="3" t="s">
-        <v>176</v>
-      </c>
       <c r="D35" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>42</v>
@@ -3209,24 +3176,24 @@
         <v>22</v>
       </c>
       <c r="H35" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="I35" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="I35" s="3" t="s">
-        <v>178</v>
-      </c>
       <c r="J35" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>49</v>
@@ -3239,24 +3206,24 @@
         <v>22</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I36" s="3" t="s">
         <v>87</v>
       </c>
       <c r="J36" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B37" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>182</v>
-      </c>
       <c r="C37" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>49</v>
@@ -3269,54 +3236,54 @@
         <v>22</v>
       </c>
       <c r="H37" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="I37" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="I37" s="3" t="s">
-        <v>184</v>
-      </c>
       <c r="J37" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>185</v>
+        <v>92</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>156</v>
+        <v>139</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H38" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="I38" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="I38" s="3" t="s">
-        <v>187</v>
-      </c>
       <c r="J38" s="3">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>189</v>
+        <v>170</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>49</v>
@@ -3329,24 +3296,24 @@
         <v>22</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="J39" s="3">
-        <v>5</v>
+        <v>65</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>192</v>
+        <v>142</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>193</v>
+        <v>136</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>49</v>
@@ -3359,57 +3326,57 @@
         <v>22</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>87</v>
+        <v>186</v>
       </c>
       <c r="J40" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>123</v>
+        <v>49</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>199</v>
+        <v>87</v>
       </c>
       <c r="J41" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>171</v>
+        <v>197</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>156</v>
+        <v>198</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>37</v>
@@ -3419,27 +3386,27 @@
         <v>22</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="J42" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>204</v>
+        <v>49</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>37</v>
@@ -3449,87 +3416,87 @@
         <v>22</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>87</v>
+        <v>203</v>
       </c>
       <c r="J43" s="3">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>167</v>
+        <v>205</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>208</v>
+        <v>49</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>169</v>
+        <v>186</v>
       </c>
       <c r="J44" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>47</v>
+        <v>92</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>137</v>
+        <v>208</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>49</v>
+        <v>209</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>148</v>
+        <v>87</v>
       </c>
       <c r="J45" s="3">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>98</v>
+        <v>211</v>
       </c>
       <c r="B46" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="C46" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="C46" s="3" t="s">
-        <v>197</v>
-      </c>
       <c r="D46" s="3" t="s">
-        <v>123</v>
+        <v>213</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>37</v>
@@ -3539,24 +3506,24 @@
         <v>22</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="J46" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>214</v>
+        <v>47</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>215</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>49</v>
@@ -3572,24 +3539,24 @@
         <v>216</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="J47" s="3">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="B48" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C48" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="C48" s="3" t="s">
-        <v>218</v>
-      </c>
       <c r="D48" s="3" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>37</v>
@@ -3599,54 +3566,54 @@
         <v>22</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>91</v>
+        <v>124</v>
       </c>
       <c r="J48" s="3">
-        <v>44</v>
+        <v>22</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>47</v>
+        <v>92</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>140</v>
+        <v>198</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="J49" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>47</v>
+        <v>221</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>222</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>193</v>
+        <v>155</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>49</v>
@@ -3662,21 +3629,21 @@
         <v>223</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="J50" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>224</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>140</v>
+        <v>225</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>49</v>
@@ -3689,24 +3656,24 @@
         <v>22</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>199</v>
+        <v>91</v>
       </c>
       <c r="J51" s="3">
-        <v>6</v>
+        <v>45</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>226</v>
+        <v>47</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>227</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>156</v>
+        <v>139</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>49</v>
@@ -3722,57 +3689,57 @@
         <v>228</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>69</v>
+        <v>168</v>
       </c>
       <c r="J52" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B53" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="B53" s="3" t="s">
-        <v>230</v>
-      </c>
       <c r="C53" s="3" t="s">
-        <v>156</v>
+        <v>194</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="J53" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B54" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="B54" s="3" t="s">
-        <v>196</v>
-      </c>
       <c r="C54" s="3" t="s">
-        <v>197</v>
+        <v>155</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>123</v>
+        <v>49</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
@@ -3782,10 +3749,10 @@
         <v>233</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>199</v>
+        <v>69</v>
       </c>
       <c r="J54" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3796,37 +3763,37 @@
         <v>235</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>236</v>
+        <v>155</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>123</v>
+        <v>49</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>238</v>
+        <v>168</v>
       </c>
       <c r="J55" s="3">
-        <v>24</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>49</v>
@@ -3839,24 +3806,24 @@
         <v>22</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="I56" s="3" t="s">
         <v>87</v>
       </c>
       <c r="J56" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>49</v>
@@ -3869,24 +3836,24 @@
         <v>22</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="J57" s="3">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>53</v>
+        <v>244</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>49</v>
@@ -3899,24 +3866,24 @@
         <v>22</v>
       </c>
       <c r="H58" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="I58" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="I58" s="3" t="s">
-        <v>248</v>
-      </c>
       <c r="J58" s="3">
-        <v>65</v>
+        <v>44</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>249</v>
+        <v>53</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>251</v>
+        <v>136</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>49</v>
@@ -3924,31 +3891,29 @@
       <c r="E59" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F59" s="3" t="s">
-        <v>252</v>
-      </c>
+      <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>169</v>
+        <v>250</v>
       </c>
       <c r="J59" s="3">
-        <v>1</v>
+        <v>66</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>182</v>
+        <v>252</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>137</v>
+        <v>253</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>49</v>
@@ -3956,7 +3921,9 @@
       <c r="E60" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F60" s="3"/>
+      <c r="F60" s="3" t="s">
+        <v>254</v>
+      </c>
       <c r="G60" s="3" t="s">
         <v>22</v>
       </c>
@@ -3964,7 +3931,7 @@
         <v>255</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>87</v>
+        <v>168</v>
       </c>
       <c r="J60" s="3">
         <v>2</v>
@@ -3975,103 +3942,105 @@
         <v>256</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>257</v>
+        <v>174</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>137</v>
+        <v>175</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>69</v>
+        <v>189</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>65</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>98</v>
+        <v>66</v>
       </c>
       <c r="B62" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H62" s="3" t="s">
         <v>259</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F62" s="3"/>
-      <c r="G62" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>260</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>69</v>
       </c>
       <c r="J62" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>176</v>
+        <v>136</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>123</v>
+        <v>49</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>263</v>
+        <v>165</v>
       </c>
       <c r="J63" s="3">
-        <v>64</v>
+        <v>4</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>137</v>
+        <v>198</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>42</v>
@@ -4081,56 +4050,54 @@
         <v>22</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>267</v>
+        <v>87</v>
       </c>
       <c r="J64" s="3">
-        <v>22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>66</v>
+        <v>265</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>49</v>
+        <v>151</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F65" s="3" t="s">
-        <v>113</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="J65" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>270</v>
+        <v>92</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>182</v>
+        <v>268</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>137</v>
+        <v>155</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>49</v>
@@ -4143,27 +4110,27 @@
         <v>22</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>166</v>
+        <v>69</v>
       </c>
       <c r="J66" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>197</v>
+        <v>136</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>123</v>
+        <v>49</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>42</v>
@@ -4173,84 +4140,84 @@
         <v>22</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>87</v>
+        <v>165</v>
       </c>
       <c r="J67" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>275</v>
+        <v>47</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>152</v>
+        <v>49</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="J68" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>279</v>
+        <v>241</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="J69" s="3">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>49</v>
@@ -4263,10 +4230,10 @@
         <v>22</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>166</v>
+        <v>87</v>
       </c>
       <c r="J70" s="3">
         <v>3</v>
@@ -4274,13 +4241,13 @@
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>193</v>
+        <v>136</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>49</v>
@@ -4293,54 +4260,54 @@
         <v>22</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
       <c r="J71" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>47</v>
+        <v>283</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>69</v>
+        <v>168</v>
       </c>
       <c r="J72" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>49</v>
@@ -4353,84 +4320,84 @@
         <v>22</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="I73" s="3" t="s">
         <v>87</v>
       </c>
       <c r="J73" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>169</v>
+        <v>124</v>
       </c>
       <c r="J74" s="3">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F75" s="3"/>
       <c r="G75" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="J75" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>49</v>
@@ -4443,24 +4410,24 @@
         <v>22</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>125</v>
+        <v>87</v>
       </c>
       <c r="J76" s="3">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>301</v>
+        <v>283</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>137</v>
+        <v>194</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>49</v>
@@ -4473,27 +4440,27 @@
         <v>22</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>87</v>
+        <v>299</v>
       </c>
       <c r="J77" s="3">
-        <v>2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>193</v>
+        <v>302</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>37</v>
@@ -4503,27 +4470,27 @@
         <v>22</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>267</v>
+        <v>165</v>
       </c>
       <c r="J78" s="3">
-        <v>22</v>
+        <v>4</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>308</v>
+        <v>198</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>37</v>
@@ -4533,54 +4500,56 @@
         <v>22</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>166</v>
+        <v>69</v>
       </c>
       <c r="J79" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H80" s="3" t="s">
         <v>310</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="D80" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E80" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F80" s="3"/>
-      <c r="G80" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H80" s="3" t="s">
-        <v>312</v>
       </c>
       <c r="I80" s="3" t="s">
         <v>69</v>
       </c>
       <c r="J80" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>193</v>
+        <v>253</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>49</v>
@@ -4588,47 +4557,45 @@
       <c r="E81" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F81" s="3" t="s">
-        <v>315</v>
-      </c>
+      <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>69</v>
+        <v>168</v>
       </c>
       <c r="J81" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>251</v>
+        <v>155</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>169</v>
+        <v>69</v>
       </c>
       <c r="J82" s="3">
         <v>1</v>
@@ -4636,13 +4603,13 @@
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>49</v>
@@ -4655,86 +4622,86 @@
         <v>22</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="J83" s="3">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>301</v>
+        <v>320</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>156</v>
+        <v>198</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F84" s="3"/>
+      <c r="F84" s="3" t="s">
+        <v>322</v>
+      </c>
       <c r="G84" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="I84" s="3" t="s">
         <v>69</v>
       </c>
       <c r="J84" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>197</v>
+        <v>217</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>123</v>
+        <v>36</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F85" s="3" t="s">
-        <v>328</v>
-      </c>
+      <c r="F85" s="3"/>
       <c r="G85" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="I85" s="3" t="s">
         <v>69</v>
       </c>
       <c r="J85" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>330</v>
+        <v>211</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>332</v>
+        <v>217</v>
       </c>
       <c r="D86" s="3" t="s">
         <v>36</v>
@@ -4747,40 +4714,40 @@
         <v>22</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="I86" s="3" t="s">
         <v>69</v>
       </c>
       <c r="J86" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>206</v>
+        <v>231</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>332</v>
+        <v>136</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F87" s="3"/>
       <c r="G87" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>69</v>
+        <v>186</v>
       </c>
       <c r="J87" s="3">
         <v>0</v>
@@ -4788,13 +4755,13 @@
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D88" s="3" t="s">
         <v>49</v>
@@ -4807,24 +4774,24 @@
         <v>22</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="I88" s="3" t="s">
         <v>60</v>
       </c>
       <c r="J88" s="3">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>287</v>
+        <v>273</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>49</v>
@@ -4837,27 +4804,27 @@
         <v>22</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>187</v>
+        <v>336</v>
       </c>
       <c r="J89" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>37</v>
@@ -4867,27 +4834,27 @@
         <v>22</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="J90" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>42</v>
@@ -4897,24 +4864,24 @@
         <v>22</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="J91" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D92" s="3" t="s">
         <v>49</v>
@@ -4927,24 +4894,24 @@
         <v>22</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>267</v>
+        <v>299</v>
       </c>
       <c r="J92" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D93" s="3" t="s">
         <v>49</v>
@@ -4957,27 +4924,27 @@
         <v>22</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>169</v>
+        <v>186</v>
       </c>
       <c r="J93" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>356</v>
+        <v>172</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>197</v>
+        <v>155</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>123</v>
+        <v>49</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>37</v>
@@ -4987,42 +4954,40 @@
         <v>22</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>178</v>
+        <v>87</v>
       </c>
       <c r="J94" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>311</v>
+        <v>354</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>197</v>
+        <v>355</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>123</v>
+        <v>151</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F95" s="3" t="s">
-        <v>359</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="F95" s="3"/>
       <c r="G95" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>166</v>
+        <v>87</v>
       </c>
       <c r="J95" s="3">
         <v>3</v>
@@ -5030,128 +4995,38 @@
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H96" s="3" t="s">
         <v>361</v>
-      </c>
-      <c r="B96" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="C96" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="D96" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E96" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F96" s="3"/>
-      <c r="G96" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H96" s="3" t="s">
-        <v>362</v>
       </c>
       <c r="I96" s="3" t="s">
         <v>87</v>
       </c>
       <c r="J96" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="B97" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="C97" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="D97" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E97" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F97" s="3"/>
-      <c r="G97" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H97" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="I97" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="J97" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="B98" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="C98" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="D98" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="E98" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F98" s="3"/>
-      <c r="G98" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H98" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="I98" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="J98" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="B99" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="C99" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="D99" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E99" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F99" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="G99" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H99" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="I99" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="J99" s="3">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J99"/>
+  <autoFilter ref="A1:J96"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5248,9 +5123,6 @@
     <hyperlink ref="H94" r:id="rId93"/>
     <hyperlink ref="H95" r:id="rId94"/>
     <hyperlink ref="H96" r:id="rId95"/>
-    <hyperlink ref="H97" r:id="rId96"/>
-    <hyperlink ref="H98" r:id="rId97"/>
-    <hyperlink ref="H99" r:id="rId98"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5258,8 +5130,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="56" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="1" max="1" width="40" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -5292,32 +5164,32 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>62</v>
+        <v>184</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>49</v>
+        <v>139</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>68</v>
+        <v>185</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>47</v>
+        <v>190</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>173</v>
+        <v>142</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -5325,18 +5197,18 @@
         <v>22</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>174</v>
+        <v>191</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>226</v>
+        <v>204</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>227</v>
+        <v>205</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>156</v>
+        <v>194</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -5344,18 +5216,18 @@
         <v>22</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>228</v>
+        <v>206</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>256</v>
+        <v>275</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>257</v>
+        <v>241</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5363,18 +5235,18 @@
         <v>22</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>98</v>
+        <v>280</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>259</v>
+        <v>281</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -5382,18 +5254,18 @@
         <v>22</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>260</v>
+        <v>282</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>66</v>
+        <v>231</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>268</v>
+        <v>329</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -5401,18 +5273,18 @@
         <v>22</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>269</v>
+        <v>330</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>47</v>
+        <v>349</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>287</v>
+        <v>166</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>156</v>
+        <v>194</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -5420,125 +5292,11 @@
         <v>22</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>335</v>
+        <v>350</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G14"/>
+  <autoFilter ref="A1:G8"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -5547,12 +5305,6 @@
     <hyperlink ref="G6" r:id="rId5"/>
     <hyperlink ref="G7" r:id="rId6"/>
     <hyperlink ref="G8" r:id="rId7"/>
-    <hyperlink ref="G9" r:id="rId8"/>
-    <hyperlink ref="G10" r:id="rId9"/>
-    <hyperlink ref="G11" r:id="rId10"/>
-    <hyperlink ref="G12" r:id="rId11"/>
-    <hyperlink ref="G13" r:id="rId12"/>
-    <hyperlink ref="G14" r:id="rId13"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5566,23 +5318,23 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>373</v>
+        <v>362</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>374</v>
+        <v>363</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>315</v>
+        <v>364</v>
       </c>
       <c r="B2" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="B3" s="3">
         <v>15</v>
@@ -5590,31 +5342,31 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>376</v>
+        <v>309</v>
       </c>
       <c r="B4" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B5" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B6" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>328</v>
+        <v>366</v>
       </c>
       <c r="B7" s="3">
         <v>9</v>
@@ -5622,7 +5374,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>377</v>
+        <v>322</v>
       </c>
       <c r="B8" s="3">
         <v>9</v>
@@ -5630,15 +5382,15 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>378</v>
+        <v>367</v>
       </c>
       <c r="B9" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>379</v>
+        <v>368</v>
       </c>
       <c r="B10" s="3">
         <v>8</v>
@@ -5646,7 +5398,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B11" s="3">
         <v>8</v>
@@ -5654,7 +5406,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>380</v>
+        <v>369</v>
       </c>
       <c r="B12" s="3">
         <v>7</v>
@@ -5662,23 +5414,23 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>381</v>
+        <v>370</v>
       </c>
       <c r="B13" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>382</v>
+        <v>371</v>
       </c>
       <c r="B14" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>383</v>
+        <v>372</v>
       </c>
       <c r="B15" s="3">
         <v>6</v>
@@ -5686,7 +5438,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>384</v>
+        <v>373</v>
       </c>
       <c r="B16" s="3">
         <v>5</v>
@@ -5699,7 +5451,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5708,7 +5460,7 @@
         <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>385</v>
+        <v>374</v>
       </c>
     </row>
     <row r="2">
@@ -5737,7 +5489,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>93</v>
+        <v>166</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -5745,7 +5497,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -5753,23 +5505,23 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>175</v>
+        <v>48</v>
       </c>
       <c r="B7" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>182</v>
+        <v>93</v>
       </c>
       <c r="B8" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>48</v>
+        <v>101</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
@@ -5777,7 +5529,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -5785,7 +5537,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>171</v>
+        <v>142</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5793,7 +5545,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5801,7 +5553,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>196</v>
+        <v>172</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5809,7 +5561,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>287</v>
+        <v>181</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -5817,7 +5569,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>311</v>
+        <v>241</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -5825,7 +5577,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>327</v>
+        <v>273</v>
       </c>
       <c r="B16" s="3">
         <v>2</v>
@@ -5839,23 +5591,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>386</v>
+        <v>375</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>387</v>
+        <v>376</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>385</v>
+        <v>374</v>
       </c>
     </row>
     <row r="2">
@@ -5891,10 +5643,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>93</v>
+        <v>34</v>
       </c>
       <c r="C4" s="3">
-        <v>9.2</v>
+        <v>7.1</v>
       </c>
       <c r="D4" s="3">
         <v>3</v>
@@ -5905,13 +5657,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>34</v>
+        <v>101</v>
       </c>
       <c r="C5" s="3">
-        <v>7.1</v>
+        <v>7.0</v>
       </c>
       <c r="D5" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -5919,10 +5671,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>48</v>
+        <v>93</v>
       </c>
       <c r="C6" s="3">
-        <v>6.0</v>
+        <v>6.2</v>
       </c>
       <c r="D6" s="3">
         <v>2</v>
@@ -5933,13 +5685,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>182</v>
+        <v>48</v>
       </c>
       <c r="C7" s="3">
-        <v>4.2</v>
+        <v>6.0</v>
       </c>
       <c r="D7" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -5947,13 +5699,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>112</v>
+        <v>174</v>
       </c>
       <c r="C8" s="3">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="D8" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -5961,13 +5713,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>167</v>
+        <v>111</v>
       </c>
       <c r="C9" s="3">
         <v>3.6</v>
       </c>
       <c r="D9" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -5975,7 +5727,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="C10" s="3">
         <v>3.6</v>
@@ -6003,7 +5755,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C12" s="3">
         <v>2.8</v>
@@ -6017,7 +5769,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>173</v>
+        <v>281</v>
       </c>
       <c r="C13" s="3">
         <v>2.8</v>
@@ -6031,13 +5783,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>311</v>
+        <v>126</v>
       </c>
       <c r="C14" s="3">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="D14" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -6045,10 +5797,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>327</v>
+        <v>142</v>
       </c>
       <c r="C15" s="3">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="D15" s="3">
         <v>2</v>
@@ -6059,13 +5811,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>127</v>
+        <v>170</v>
       </c>
       <c r="C16" s="3">
         <v>2.4</v>
       </c>
       <c r="D16" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -6085,21 +5837,21 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>389</v>
+        <v>378</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>390</v>
+        <v>379</v>
       </c>
       <c r="B2" s="3">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>391</v>
+        <v>380</v>
       </c>
     </row>
     <row r="3">
@@ -6107,10 +5859,10 @@
         <v>37</v>
       </c>
       <c r="B3" s="3">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>392</v>
+        <v>381</v>
       </c>
     </row>
     <row r="4">
@@ -6121,7 +5873,7 @@
         <v>51</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>393</v>
+        <v>382</v>
       </c>
     </row>
   </sheetData>
@@ -6140,7 +5892,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
     </row>
     <row r="2">
@@ -6153,10 +5905,10 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B3" s="3">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
@@ -6164,12 +5916,12 @@
         <v>36</v>
       </c>
       <c r="B4" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -6177,15 +5929,15 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B7" s="3">
         <v>1</v>
@@ -6193,7 +5945,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="B8" s="3">
         <v>1</v>
@@ -6201,7 +5953,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="B9" s="3">
         <v>1</v>
@@ -6228,10 +5980,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>386</v>
+        <v>375</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>394</v>
+        <v>383</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>25</v>
@@ -6243,10 +5995,10 @@
         <v>27</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>395</v>
+        <v>384</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>396</v>
+        <v>385</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>20</v>
@@ -6263,7 +6015,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>397</v>
+        <v>386</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>56</v>
@@ -6272,22 +6024,22 @@
         <v>57</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>398</v>
+        <v>387</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>399</v>
+        <v>388</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>400</v>
+        <v>389</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>401</v>
+        <v>203</v>
       </c>
     </row>
     <row r="3">
@@ -6295,31 +6047,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>402</v>
+        <v>390</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>403</v>
+        <v>391</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>404</v>
+        <v>392</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>405</v>
+        <v>393</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>406</v>
+        <v>394</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>408</v>
+        <v>396</v>
       </c>
     </row>
     <row r="4">
@@ -6327,28 +6079,28 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>409</v>
+        <v>397</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>410</v>
+        <v>398</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>405</v>
+        <v>393</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>411</v>
+        <v>399</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>412</v>
+        <v>400</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>73</v>
@@ -6359,31 +6111,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>413</v>
+        <v>401</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>414</v>
+        <v>402</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>415</v>
+        <v>403</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>405</v>
+        <v>393</v>
       </c>
       <c r="F5" s="3">
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>416</v>
+        <v>404</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>417</v>
+        <v>405</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="6">
@@ -6391,31 +6143,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>358</v>
+        <v>406</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>324</v>
+        <v>407</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="F6" s="3">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
     </row>
     <row r="7">
@@ -6423,31 +6175,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>422</v>
+        <v>413</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>423</v>
+        <v>414</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>424</v>
+        <v>212</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>425</v>
+        <v>393</v>
       </c>
       <c r="F7" s="3">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>426</v>
+        <v>415</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>427</v>
+        <v>416</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>428</v>
+        <v>203</v>
       </c>
     </row>
     <row r="8">
@@ -6455,31 +6207,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>429</v>
+        <v>417</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>430</v>
+        <v>174</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>207</v>
+        <v>175</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>405</v>
+        <v>393</v>
       </c>
       <c r="F8" s="3">
         <v>84</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>431</v>
+        <v>418</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>432</v>
+        <v>419</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>401</v>
+        <v>420</v>
       </c>
     </row>
     <row r="9">
@@ -6487,31 +6239,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>433</v>
+        <v>421</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>175</v>
+        <v>422</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>176</v>
+        <v>194</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>405</v>
+        <v>423</v>
       </c>
       <c r="F9" s="3">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>434</v>
+        <v>424</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
     </row>
     <row r="10">
@@ -6519,31 +6271,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>193</v>
+        <v>136</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>439</v>
+        <v>393</v>
       </c>
       <c r="F10" s="3">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>97</v>
+        <v>431</v>
       </c>
     </row>
     <row r="11">
@@ -6551,31 +6303,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>442</v>
+        <v>432</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>443</v>
+        <v>433</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>137</v>
+        <v>434</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>405</v>
+        <v>387</v>
       </c>
       <c r="F11" s="3">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>444</v>
+        <v>435</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>445</v>
+        <v>436</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>446</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12">
@@ -6583,31 +6335,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>447</v>
+        <v>437</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>448</v>
+        <v>422</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>449</v>
+        <v>194</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>398</v>
+        <v>423</v>
       </c>
       <c r="F12" s="3">
         <v>74</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>450</v>
+        <v>438</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>451</v>
+        <v>439</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>46</v>
+        <v>420</v>
       </c>
     </row>
     <row r="13">
@@ -6615,31 +6367,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>452</v>
+        <v>440</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>193</v>
+        <v>442</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>439</v>
+        <v>423</v>
       </c>
       <c r="F13" s="3">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>436</v>
+        <v>73</v>
       </c>
     </row>
     <row r="14">
@@ -6647,31 +6399,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>456</v>
+        <v>446</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>332</v>
+        <v>217</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>439</v>
+        <v>423</v>
       </c>
       <c r="F14" s="3">
         <v>70</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>457</v>
+        <v>447</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>458</v>
+        <v>448</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="15">
@@ -6679,31 +6431,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>459</v>
+        <v>449</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>461</v>
+        <v>451</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>405</v>
+        <v>393</v>
       </c>
       <c r="F15" s="3">
         <v>68</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>462</v>
+        <v>452</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>463</v>
+        <v>453</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
     </row>
     <row r="16">
@@ -6711,28 +6463,28 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>465</v>
+        <v>455</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>466</v>
+        <v>456</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>398</v>
+        <v>387</v>
       </c>
       <c r="F16" s="3">
         <v>61</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>468</v>
+        <v>458</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>65</v>
@@ -6743,31 +6495,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>469</v>
+        <v>459</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>367</v>
+        <v>355</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>425</v>
+        <v>409</v>
       </c>
       <c r="F17" s="3">
         <v>57</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>471</v>
+        <v>461</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>472</v>
+        <v>462</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="18">
@@ -6775,28 +6527,28 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>473</v>
+        <v>463</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>356</v>
+        <v>464</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>405</v>
+        <v>393</v>
       </c>
       <c r="F18" s="3">
         <v>52</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>474</v>
+        <v>465</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>475</v>
+        <v>466</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>87</v>
@@ -6807,31 +6559,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>476</v>
+        <v>467</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>477</v>
+        <v>468</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>478</v>
+        <v>469</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>405</v>
+        <v>393</v>
       </c>
       <c r="F19" s="3">
         <v>48</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>479</v>
+        <v>470</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="20">
@@ -6839,31 +6591,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>482</v>
+        <v>473</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>156</v>
+        <v>198</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="F20" s="3">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>483</v>
+        <v>474</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>484</v>
+        <v>475</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>87</v>
+        <v>153</v>
       </c>
     </row>
     <row r="21">
@@ -6871,31 +6623,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>485</v>
+        <v>476</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>486</v>
+        <v>305</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>425</v>
+        <v>393</v>
       </c>
       <c r="F21" s="3">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>487</v>
+        <v>477</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>488</v>
+        <v>478</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>154</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W44.xlsx
+++ b/reports/devops-jobs-israel-2026-W44.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="496">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="515">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-29T12:48:33</t>
+    <t xml:space="preserve">2026-10-30T12:40:21</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -57,12 +57,15 @@
     <t xml:space="preserve">Junior %</t>
   </si>
   <si>
+    <t xml:space="preserve">1.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salary disclosure rate %</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.0%</t>
   </si>
   <si>
-    <t xml:space="preserve">Salary disclosure rate %</t>
-  </si>
-  <si>
     <t xml:space="preserve">Maintained by</t>
   </si>
   <si>
@@ -426,22 +429,34 @@
     <t xml:space="preserve">https://orca.security/about/careers/6149333004?gh_jid=6149333004</t>
   </si>
   <si>
-    <t xml:space="preserve">Aidoc</t>
+    <t xml:space="preserve">Mentee Robotics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-mentee-robotics-4481407411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bitsight</t>
   </si>
   <si>
     <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-aidoc-4465646027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentee Robotics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-mentee-robotics-4481407411</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-bitsight-4485279583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AITAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-aitan-4484116721</t>
   </si>
   <si>
     <t xml:space="preserve">Senior DevOps Platform Engineer- CTI</t>
@@ -453,990 +468,1029 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-platform-engineer-cti-at-dream-4465727084</t>
   </si>
   <si>
+    <t xml:space="preserve">Sr. DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harmonic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-harmonic-4360460066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deloitte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-deloitte-4479294849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pango</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-devops-engineer-at-pango-4481441009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Point Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-check-point-software-4483375334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logica-IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-logica-it-4482293600</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simplex 3D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-devops-engineer-at-simplex-3d-4449504561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stealth AI Startup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-stealth-ai-startup-4484130196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BigID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-bigid-4482680687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4461883247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer - Cloud Infra Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-infra-team-at-wix-4480881694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CommBox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-commbox-4484931014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer - Data Platform (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-data-platform-cortex-at-palo-alto-networks-4455871961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer- Detection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-detection-at-dream-4484937206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Devops Engineer - AI Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bridgewise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-ai-team-at-bridgewise-4482680803</t>
+  </si>
+  <si>
     <t xml:space="preserve">Priority Software</t>
   </si>
   <si>
     <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-priority-software-4477000056</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-priority-software-4484524283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform DevOps Engineer - Core Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jeen.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-devops-engineer-core-platform-at-jeen-ai-4482092082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checkmarx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-checkmarx-4439196775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IRONSCALES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-ironscales-4483869791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Speedata.io</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-speedata-io-4483379335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal DevOps Engineer (Cortex Agentix Endpoint Security)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-cortex-agentix-endpoint-security-at-palo-alto-networks-4418753719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zenity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-zenity-4478465745</t>
   </si>
   <si>
     <t xml:space="preserve">2026-10-15</t>
   </si>
   <si>
-    <t xml:space="preserve">Sr. DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harmonic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-harmonic-4360460066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deloitte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-deloitte-4479294849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pango</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-devops-engineer-at-pango-4481441009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check Point Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-check-point-software-4483375334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-25</t>
+    <t xml:space="preserve">Zscaler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-zscaler-4465317702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4474645372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4481079700</t>
   </si>
   <si>
     <t xml:space="preserve">comblack</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-comblack-4483574435</t>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-comblack-4484958840</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Technical Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FlightOps.io</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-technical-lead-at-flightops-io-4482594710</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-engineer-at-comblack-4484971419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personetics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-personetics-4428829912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeValue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-codevalue-4483726365</t>
   </si>
   <si>
     <t xml:space="preserve">2026-10-27</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior Principal DevOps Engineer (Cortex Cloud)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-devops-engineer-cortex-cloud-at-palo-alto-networks-4443693726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logica-IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-logica-it-4482293600</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
+    <t xml:space="preserve">Senior Cloud Infrastructure Engineer- Q</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-infrastructure-engineer-q-at-apple-4484157831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Talent Integration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-talent-integration-4481088382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-sqlink-group-4482292829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Webiks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-reliability-engineer-at-webiks-4483579517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineering - Storage</t>
   </si>
   <si>
     <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-4481638138</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineering-storage-at-nvidia-4457190574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-nvidia-4458308805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/observability-platform-team-lead-at-gong-4484452499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE / DevOps Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">april</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-devops-lead-at-april-4416179005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure Engineer - Core Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-core-systems-at-wix-4483368404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infra Engineer Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infra-engineer-team-lead-at-dialog-4481085538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SciPlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-sciplay-4391151881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-stealth-ai-startup-4484130164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Software Engineer, DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aiven</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-software-engineer-devops-at-aiven-4484502847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software System Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-system-reliability-engineer-at-cisco-4483388333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oriient</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-oriient-4484447442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Software Engineer -Platform Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viz.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-software-engineer-platform-team-at-viz-ai-4437383686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Data Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-data-infrastructure-engineer-at-evoke-4462157157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sunbit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-sunbit-4484439423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Data Infrastructure Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-data-infrastructure-team-leader-at-evoke-4484943062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Platform Engineer (Infra Platform)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">monday.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-infra-platform-at-monday-com-4483388052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal DevOps Engineer (DexEx Platform)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-dexex-platform-at-palo-alto-networks-4483063503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI &amp; Software Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BioCatch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-software-infra-engineer-at-biocatch-4484927514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ScaleOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-scaleops-4483763089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior GPU Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zesty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-gpu-platform-engineer-at-zesty-4481405125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior AI &amp; Software Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-software-infra-engineer-at-biocatch-4447894244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Backend Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claroty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/backend-platform-engineer-at-claroty-4482292784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Millennium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-millennium-4482698329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-alice-formerly-activefence-4472729462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Platform Engineer (Mid-level)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobgether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-mid-level-at-jobgether-4481691238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guesty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-platform-engineer-at-guesty-4473205757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OpenShift Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential Careers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/openshift-platform-engineer-at-confidential-careers-4482299668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Agentic AI Engineer (AWS/DevOps)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Directeam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-agentic-ai-engineer-aws-devops-at-directeam-4482501198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Developer (DevOps and Infrastructure)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rapyd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-developer-devops-and-infrastructure-at-rapyd-4475489875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal Data Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MediaForce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-data-platform-engineer-at-mediaforce-4481460917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Infrastructure &amp; Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moon Active</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-cloud-engineer-at-moon-active-4447031167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calanit by one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-calanit-by-one-4484447830</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure Infrastructure Engineer – AI &amp; Automation (5524)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INGIMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/azure-infrastructure-engineer-%E2%80%93-ai-automation-5524-at-ingima-4484427543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integress, Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-engineer-at-integress-inc-4483842402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SR DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-bitsight-4483570331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Founding DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stealth-Mode Cybersecurity Startup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/founding-devops-at-stealth-mode-cybersecurity-startup-4482932513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prisma Photonics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-prisma-photonics-4432235322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-engineer-at-cato-networks-4463471007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Integration &amp; Infrastructure Engineer (Advanced storage infrastructure for AI workloads)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sandisk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-integration-infrastructure-engineer-advanced-storage-infrastructure-for-ai-workloads-at-sandisk-4478351208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moveo Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-infrastructure-engineer-at-moveo-source-4480775799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-elbit-systems-israel-4474036853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wayve</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-wayve-4474417523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OpenShift Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/openshift-infrastructure-engineer-at-comblack-4484951649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-infrastructure-engineer-at-logica-it-4481435276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E2E Solutions IL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-e2e-solutions-il-4482928669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developer Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=8264438&amp;gh_jid=8264438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Development Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clarivate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/development-operations-engineer-at-clarivate-4467992253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BLE System Test DevOps Intern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Texas Instruments Europe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ble-system-test-devops-intern-at-texas-instruments-europe-4484112036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux &amp; HPC Systems Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Novocure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tirat HaCarmel, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-hpc-systems-engineer-at-novocure-4478872342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System &amp; Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-infrastructure-engineer-at-final-4475581791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cross River</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-at-cross-river-4478788112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HPC Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4471977303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Monitoring Engineer (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-monitoring-engineer-student-position-at-upwind-security-4476759903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Technical Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security Analyst (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/security-analyst-student-position-at-upwind-security-4473525994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Integration Student, SPIV team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annapurna Labs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-integration-student-spiv-team-at-annapurna-labs-4456348779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student Software Engineer – Cloud, Big Data, Billing &amp; AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Cloud (any), Docker, Kubernetes, CI/CD, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-software-engineer-%E2%80%93-cloud-big-data-billing-ai-at-sap-4476596020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kela Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior CAD Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cad-engineer-university-graduate-google-cloud-at-google-4483213993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator (37866)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-37866-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4483535843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator Tier 3 – IT Infrastructure &amp; Cybersecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mornex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-tier-3-%E2%80%93-it-infrastructure-cybersecurity-at-mornex-4474264582</t>
   </si>
   <si>
     <t xml:space="preserve">2026-10-23</t>
   </si>
   <si>
-    <t xml:space="preserve">BigID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-bigid-4482680687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer - Cloud Infra Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-infra-team-at-wix-4480881694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CommBox</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-commbox-4484931014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer - Data Platform (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-data-platform-cortex-at-palo-alto-networks-4455871961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer- Detection</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-detection-at-dream-4484937206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Devops Engineer - AI Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bridgewise</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-ai-team-at-bridgewise-4482680803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform DevOps Engineer - Core Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jeen.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-devops-engineer-core-platform-at-jeen-ai-4482092082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Checkmarx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-checkmarx-4439196775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IRONSCALES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-ironscales-4483869791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Speedata.io</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-speedata-io-4483379335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-engineer-at-comblack-4483582140</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zenity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-zenity-4478465745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4474645372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4481079700</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SR DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bitsight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-bitsight-4483570331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Personetics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-personetics-4428829912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeValue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-codevalue-4483726365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elementor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-elementor-4482868447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-sqlink-group-4482292829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Webiks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-reliability-engineer-at-webiks-4483579517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Founding DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stealth-Mode Cybersecurity Startup</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/founding-devops-at-stealth-mode-cybersecurity-startup-4482932513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Data Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-data-infrastructure-engineer-at-evoke-4462157157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE / DevOps Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">april</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-devops-lead-at-april-4416179005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SciPlay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-sciplay-4391151881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevSecOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PayPlus - The Future of Payments &amp; Commerce</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devsecops-engineer-at-payplus-the-future-of-payments-commerce-4482999139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineering - Storage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineering-storage-at-nvidia-4457190574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/observability-platform-team-lead-at-gong-4484452499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure Engineer - Core Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-core-systems-at-wix-4483368404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infra Engineer Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dialog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infra-engineer-team-lead-at-dialog-4481085538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software System Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-system-reliability-engineer-at-cisco-4483388333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oriient</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-oriient-4484447442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Software Engineer -Platform Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viz.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-software-engineer-platform-team-at-viz-ai-4437383686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sunbit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-sunbit-4484439423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Data Infrastructure Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-data-infrastructure-team-leader-at-evoke-4484943062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Platform Engineer (Infra Platform)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monday.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-infra-platform-at-monday-com-4483388052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI &amp; Software Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BioCatch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-software-infra-engineer-at-biocatch-4484927514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ScaleOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-scaleops-4483763089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior GPU Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zesty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-gpu-platform-engineer-at-zesty-4481405125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior AI &amp; Software Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-software-infra-engineer-at-biocatch-4447894244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claroty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-claroty-4482292784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Millennium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-millennium-4482698329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-alice-formerly-activefence-4472729462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Platform Engineer (Mid-level)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobgether</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-mid-level-at-jobgether-4481691238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OpenShift Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential Careers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/openshift-platform-engineer-at-confidential-careers-4482299668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Agentic AI Engineer (AWS/DevOps)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Directeam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-agentic-ai-engineer-aws-devops-at-directeam-4482501198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principal Data Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MediaForce</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-data-platform-engineer-at-mediaforce-4481460917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calanit by one</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-calanit-by-one-4484447830</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Infrastructure &amp; Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moon Active</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-cloud-engineer-at-moon-active-4447031167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure Infrastructure Engineer – AI &amp; Automation (5524)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INGIMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/azure-infrastructure-engineer-%E2%80%93-ai-automation-5524-at-ingima-4484427543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT DevOps Engineer - 244284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-devops-engineer-244284-at-experis-israel-4482290223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Integress, Inc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-engineer-at-integress-inc-4483842402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prisma Photonics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-prisma-photonics-4432235322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-engineer-at-cato-networks-4463471007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principal Devops &amp; Infra Tech Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-infra-tech-lead-at-sunbit-4474134295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Integration &amp; Infrastructure Engineer (Advanced storage infrastructure for AI workloads)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sandisk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-integration-infrastructure-engineer-advanced-storage-infrastructure-for-ai-workloads-at-sandisk-4478351208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moveo Source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-infrastructure-engineer-at-moveo-source-4480775799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-elbit-systems-israel-4474036853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OpenShift Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/openshift-infrastructure-engineer-at-comblack-4484951649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-infrastructure-engineer-at-logica-it-4481435276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E2E Solutions IL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-e2e-solutions-il-4482928669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JobsSeek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Midreshet Ben-Gurion, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-linux-system-administrator-at-jobsseek-4483393914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.3%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.7%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developer Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=8264438&amp;gh_jid=8264438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Development Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clarivate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/development-operations-engineer-at-clarivate-4467992253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rapyd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux &amp; HPC Systems Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Novocure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tirat HaCarmel, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-hpc-systems-engineer-at-novocure-4478872342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System &amp; Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-infrastructure-engineer-at-final-4475581791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cross River</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-at-cross-river-4478788112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HPC Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4471977303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Monitoring Engineer (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upwind Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-monitoring-engineer-student-position-at-upwind-security-4476759903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Technical Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New York City</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, GCP, Cloud (any), Git, Terraform/IaC, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/melio/jobs/7995568003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security Analyst (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/security-analyst-student-position-at-upwind-security-4473525994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Integration Student, SPIV team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Annapurna Labs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-integration-student-spiv-team-at-annapurna-labs-4456348779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student Software Engineer – Cloud, Big Data, Billing &amp; AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Cloud (any), Docker, Kubernetes, CI/CD, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-software-engineer-%E2%80%93-cloud-big-data-billing-ai-at-sap-4476596020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kela Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior CAD Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cad-engineer-university-graduate-google-cloud-at-google-4483213993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator (37866)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-37866-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4483535843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator Tier 3 – IT Infrastructure &amp; Cybersecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mornex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-tier-3-%E2%80%93-it-infrastructure-cybersecurity-at-mornex-4474264582</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
   </si>
   <si>
@@ -1473,13 +1527,16 @@
     <t xml:space="preserve">Cloud (any)</t>
   </si>
   <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
     <t xml:space="preserve">Automation</t>
   </si>
   <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform/IaC</t>
+    <t xml:space="preserve">Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git</t>
   </si>
   <si>
     <t xml:space="preserve">Elapsed (s)</t>
@@ -1631,7 +1688,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>95</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7">
@@ -1639,7 +1696,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
@@ -1647,7 +1704,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>50</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9">
@@ -1655,7 +1712,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>834</v>
+        <v>848</v>
       </c>
     </row>
     <row r="10">
@@ -1663,7 +1720,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1679,7 +1736,7 @@
         <v>13</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
@@ -1688,26 +1745,26 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -1716,23 +1773,23 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B19" s="3">
-        <v>73</v>
+        <v>82</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B20" s="3">
         <v>22</v>
@@ -1751,31 +1808,31 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>377</v>
+        <v>398</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>393</v>
+        <v>412</v>
       </c>
       <c r="B2" s="3">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>387</v>
+        <v>406</v>
       </c>
       <c r="B3" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>423</v>
+        <v>446</v>
       </c>
       <c r="B4" s="3">
         <v>6</v>
@@ -1783,7 +1840,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>409</v>
+        <v>432</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -1791,10 +1848,18 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>479</v>
+        <v>497</v>
       </c>
       <c r="B6" s="3">
         <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="B7" s="3">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1810,55 +1875,55 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>362</v>
+        <v>382</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>480</v>
+        <v>498</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>481</v>
+        <v>499</v>
       </c>
       <c r="B2" s="3">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>482</v>
+        <v>390</v>
       </c>
       <c r="B3" s="3">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>360</v>
+        <v>500</v>
       </c>
       <c r="B4" s="3">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>370</v>
+        <v>391</v>
       </c>
       <c r="B5" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>483</v>
+        <v>501</v>
       </c>
       <c r="B6" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>371</v>
+        <v>392</v>
       </c>
       <c r="B7" s="3">
         <v>20</v>
@@ -1866,15 +1931,15 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>484</v>
+        <v>502</v>
       </c>
       <c r="B8" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>485</v>
+        <v>503</v>
       </c>
       <c r="B9" s="3">
         <v>17</v>
@@ -1882,15 +1947,15 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>309</v>
+        <v>388</v>
       </c>
       <c r="B10" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>322</v>
+        <v>346</v>
       </c>
       <c r="B11" s="3">
         <v>10</v>
@@ -1898,7 +1963,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>368</v>
+        <v>385</v>
       </c>
       <c r="B12" s="3">
         <v>10</v>
@@ -1906,7 +1971,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>365</v>
+        <v>384</v>
       </c>
       <c r="B13" s="3">
         <v>10</v>
@@ -1914,15 +1979,15 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>364</v>
+        <v>329</v>
       </c>
       <c r="B14" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>486</v>
+        <v>504</v>
       </c>
       <c r="B15" s="3">
         <v>6</v>
@@ -1930,10 +1995,10 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>367</v>
+        <v>505</v>
       </c>
       <c r="B16" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1952,123 +2017,123 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>487</v>
+        <v>506</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>488</v>
+        <v>507</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>489</v>
+        <v>508</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B2" s="3">
         <v>22</v>
       </c>
       <c r="C2" s="3">
-        <v>11.8</v>
+        <v>11.3</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>490</v>
+        <v>509</v>
       </c>
       <c r="E2" s="3"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B3" s="3">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="C3" s="3">
-        <v>37.1</v>
+        <v>37.8</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>490</v>
+        <v>509</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>491</v>
+        <v>510</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>9.2</v>
+        <v>8.8</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>490</v>
+        <v>509</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>492</v>
+        <v>511</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>2.3</v>
+        <v>18.3</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>490</v>
+        <v>509</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>493</v>
+        <v>512</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>28.7</v>
+        <v>28.3</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>490</v>
+        <v>509</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>494</v>
+        <v>513</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>13.6</v>
+        <v>14.9</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>490</v>
+        <v>509</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>495</v>
+        <v>514</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>30.9</v>
+        <v>29.3</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>490</v>
+        <v>509</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2080,7 +2145,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="45" customWidth="1"/>
+    <col min="2" max="2" width="36" customWidth="1"/>
     <col min="3" max="3" width="47" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -2093,1003 +2158,1003 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="I3" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>40</v>
-      </c>
       <c r="J3" s="3">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J4" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J5" s="3">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>52</v>
-      </c>
       <c r="J6" s="3">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J7" s="3">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J8" s="3">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J9" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F10" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="J10" s="3">
         <v>71</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="J10" s="3">
-        <v>70</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J11" s="3">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J12" s="3">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J13" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J14" s="3">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J15" s="3">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J16" s="3">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="J17" s="3">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J18" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J19" s="3">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E20" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="J20" s="3">
         <v>42</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="J20" s="3">
-        <v>41</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J21" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J22" s="3">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J23" s="3">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>47</v>
+        <v>126</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="J24" s="3">
-        <v>49</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>125</v>
+        <v>93</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>87</v>
+        <v>142</v>
       </c>
       <c r="J25" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>91</v>
+        <v>142</v>
       </c>
       <c r="J26" s="3">
-        <v>45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>47</v>
+        <v>146</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>122</v>
+        <v>50</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F27" s="3"/>
       <c r="G27" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>147</v>
+        <v>92</v>
       </c>
       <c r="J27" s="3">
-        <v>14</v>
+        <v>46</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="J28" s="3">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J29" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F30" s="3"/>
       <c r="G30" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J30" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="J31" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>168</v>
+        <v>70</v>
       </c>
       <c r="J32" s="3">
         <v>2</v>
@@ -3103,116 +3168,116 @@
         <v>170</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>42</v>
+        <v>171</v>
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>73</v>
+        <v>142</v>
       </c>
       <c r="J33" s="3">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>69</v>
+        <v>142</v>
       </c>
       <c r="J34" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>47</v>
+        <v>93</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>175</v>
+        <v>140</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>122</v>
+        <v>50</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>176</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>177</v>
+        <v>88</v>
       </c>
       <c r="J35" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H36" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="I36" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="I36" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="J36" s="3">
-        <v>3</v>
+        <v>53</v>
       </c>
     </row>
     <row r="37">
@@ -3223,17 +3288,17 @@
         <v>181</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>182</v>
@@ -3242,28 +3307,28 @@
         <v>183</v>
       </c>
       <c r="J37" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>184</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>185</v>
@@ -3272,7 +3337,7 @@
         <v>186</v>
       </c>
       <c r="J38" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -3280,140 +3345,140 @@
         <v>187</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>170</v>
+        <v>188</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="J39" s="3">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I40" s="3" t="s">
         <v>186</v>
       </c>
       <c r="J40" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>194</v>
+        <v>144</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>195</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J41" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B42" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="C42" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="C42" s="3" t="s">
-        <v>198</v>
-      </c>
       <c r="D42" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>200</v>
+        <v>142</v>
       </c>
       <c r="J42" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>92</v>
+        <v>199</v>
       </c>
       <c r="B43" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C43" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="C43" s="3" t="s">
-        <v>194</v>
-      </c>
       <c r="D43" s="3" t="s">
-        <v>49</v>
+        <v>123</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>202</v>
@@ -3422,394 +3487,396 @@
         <v>203</v>
       </c>
       <c r="J43" s="3">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B44" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="B44" s="3" t="s">
-        <v>205</v>
-      </c>
       <c r="C44" s="3" t="s">
-        <v>194</v>
+        <v>144</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H44" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="I44" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>186</v>
-      </c>
       <c r="J44" s="3">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>92</v>
+        <v>207</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>208</v>
+        <v>144</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>209</v>
+        <v>50</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>87</v>
+        <v>186</v>
       </c>
       <c r="J45" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="C46" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="B46" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="C46" s="3" t="s">
+      <c r="D46" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="D46" s="3" t="s">
-        <v>213</v>
-      </c>
       <c r="E46" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>168</v>
+        <v>88</v>
       </c>
       <c r="J46" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>47</v>
+        <v>214</v>
       </c>
       <c r="B47" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F47" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="C47" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>216</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>147</v>
+        <v>78</v>
       </c>
       <c r="J47" s="3">
-        <v>14</v>
+        <v>64</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>174</v>
+        <v>217</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>217</v>
+        <v>140</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>218</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>124</v>
+        <v>219</v>
       </c>
       <c r="J48" s="3">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>92</v>
+        <v>149</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>198</v>
+        <v>140</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>122</v>
+        <v>50</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>165</v>
+        <v>61</v>
       </c>
       <c r="J49" s="3">
-        <v>4</v>
+        <v>50</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>221</v>
+        <v>93</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>222</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>155</v>
+        <v>223</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>168</v>
+        <v>125</v>
       </c>
       <c r="J50" s="3">
-        <v>2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>225</v>
+        <v>201</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>49</v>
+        <v>123</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>226</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>91</v>
+        <v>166</v>
       </c>
       <c r="J51" s="3">
-        <v>45</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>47</v>
+        <v>93</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>227</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>139</v>
+        <v>228</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>49</v>
+        <v>229</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>168</v>
+        <v>142</v>
       </c>
       <c r="J52" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>47</v>
+        <v>231</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>194</v>
+        <v>137</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="J53" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>155</v>
+        <v>201</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>49</v>
+        <v>123</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>69</v>
+        <v>142</v>
       </c>
       <c r="J54" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>234</v>
+        <v>93</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>155</v>
+        <v>237</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>168</v>
+        <v>92</v>
       </c>
       <c r="J55" s="3">
-        <v>2</v>
+        <v>46</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>237</v>
+        <v>48</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F56" s="3"/>
       <c r="G56" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>87</v>
+        <v>241</v>
       </c>
       <c r="J56" s="3">
         <v>3</v>
@@ -3817,393 +3884,391 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>243</v>
+        <v>142</v>
       </c>
       <c r="J57" s="3">
-        <v>57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>244</v>
+        <v>93</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>245</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>246</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>247</v>
+        <v>142</v>
       </c>
       <c r="J58" s="3">
-        <v>44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>53</v>
+        <v>247</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>248</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>249</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>250</v>
+        <v>70</v>
       </c>
       <c r="J59" s="3">
-        <v>66</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="B60" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="B60" s="3" t="s">
+      <c r="C60" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F60" s="3"/>
+      <c r="G60" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H60" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="C60" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="D60" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E60" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>255</v>
-      </c>
       <c r="I60" s="3" t="s">
-        <v>168</v>
+        <v>241</v>
       </c>
       <c r="J60" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>174</v>
+        <v>222</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>175</v>
+        <v>254</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="J61" s="3">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>66</v>
+        <v>256</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>258</v>
+        <v>222</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>136</v>
+        <v>254</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>49</v>
+        <v>123</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>112</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="J62" s="3">
-        <v>1</v>
+        <v>64</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>260</v>
+        <v>67</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>181</v>
+        <v>258</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F63" s="3"/>
+        <v>43</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>113</v>
+      </c>
       <c r="G63" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>165</v>
+        <v>70</v>
       </c>
       <c r="J63" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>198</v>
+        <v>140</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>122</v>
+        <v>50</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>87</v>
+        <v>263</v>
       </c>
       <c r="J64" s="3">
-        <v>3</v>
+        <v>45</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>266</v>
+        <v>181</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>151</v>
+        <v>50</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>87</v>
+        <v>166</v>
       </c>
       <c r="J65" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>92</v>
+        <v>266</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>155</v>
+        <v>201</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>49</v>
+        <v>123</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="J66" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>270</v>
+        <v>54</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="J67" s="3">
-        <v>4</v>
+        <v>67</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>47</v>
+        <v>272</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>273</v>
+        <v>173</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>69</v>
+        <v>142</v>
       </c>
       <c r="J68" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="B69" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="B69" s="3" t="s">
-        <v>241</v>
-      </c>
       <c r="C69" s="3" t="s">
-        <v>139</v>
+        <v>276</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>49</v>
+        <v>123</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>186</v>
+        <v>142</v>
       </c>
       <c r="J69" s="3">
         <v>0</v>
@@ -4211,62 +4276,62 @@
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>49</v>
+        <v>152</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J70" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>280</v>
+        <v>93</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>281</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H71" s="3" t="s">
         <v>282</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>186</v>
+        <v>70</v>
       </c>
       <c r="J71" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -4277,26 +4342,26 @@
         <v>284</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>285</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="J72" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73">
@@ -4307,83 +4372,83 @@
         <v>287</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H73" s="3" t="s">
         <v>288</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>87</v>
+        <v>289</v>
       </c>
       <c r="J73" s="3">
-        <v>3</v>
+        <v>58</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>289</v>
+        <v>48</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>124</v>
+        <v>70</v>
       </c>
       <c r="J74" s="3">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F75" s="3"/>
       <c r="G75" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H75" s="3" t="s">
         <v>293</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>69</v>
+        <v>186</v>
       </c>
       <c r="J75" s="3">
         <v>1</v>
@@ -4397,597 +4462,597 @@
         <v>295</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>296</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J76" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>283</v>
+        <v>297</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>297</v>
+        <v>188</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>194</v>
+        <v>161</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>49</v>
+        <v>162</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H77" s="3" t="s">
         <v>298</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>299</v>
+        <v>142</v>
       </c>
       <c r="J77" s="3">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="B78" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="B78" s="3" t="s">
-        <v>301</v>
-      </c>
       <c r="C78" s="3" t="s">
-        <v>302</v>
+        <v>140</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>122</v>
+        <v>50</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>165</v>
+        <v>186</v>
       </c>
       <c r="J78" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>198</v>
+        <v>140</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>122</v>
+        <v>50</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>69</v>
+        <v>241</v>
       </c>
       <c r="J79" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F80" s="3"/>
+      <c r="G80" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H80" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="B80" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="D80" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E80" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F80" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="G80" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H80" s="3" t="s">
-        <v>310</v>
-      </c>
       <c r="I80" s="3" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="J80" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>312</v>
+        <v>300</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>253</v>
+        <v>140</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>168</v>
+        <v>125</v>
       </c>
       <c r="J81" s="3">
-        <v>2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>294</v>
+        <v>310</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J82" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>319</v>
+        <v>88</v>
       </c>
       <c r="J83" s="3">
-        <v>90</v>
+        <v>4</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>320</v>
+        <v>302</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>198</v>
+        <v>144</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>122</v>
+        <v>50</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F84" s="3" t="s">
-        <v>322</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>69</v>
+        <v>318</v>
       </c>
       <c r="J84" s="3">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>217</v>
+        <v>276</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>36</v>
+        <v>123</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F85" s="3"/>
       <c r="G85" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>69</v>
+        <v>166</v>
       </c>
       <c r="J85" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>211</v>
+        <v>120</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>217</v>
+        <v>140</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F86" s="3"/>
       <c r="G86" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>69</v>
+        <v>41</v>
       </c>
       <c r="J86" s="3">
-        <v>1</v>
+        <v>31</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>231</v>
+        <v>324</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>136</v>
+        <v>201</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>49</v>
+        <v>123</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F87" s="3"/>
       <c r="G87" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>186</v>
+        <v>70</v>
       </c>
       <c r="J87" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F88" s="3"/>
+        <v>43</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>329</v>
+      </c>
       <c r="G88" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="J88" s="3">
-        <v>49</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>273</v>
+        <v>332</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F89" s="3"/>
       <c r="G89" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="J89" s="3">
         <v>22</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="J89" s="3">
-        <v>28</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="C90" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="B90" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="C90" s="3" t="s">
-        <v>339</v>
-      </c>
       <c r="D90" s="3" t="s">
-        <v>122</v>
+        <v>50</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F90" s="3"/>
       <c r="G90" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>109</v>
+        <v>241</v>
       </c>
       <c r="J90" s="3">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>343</v>
+        <v>140</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>122</v>
+        <v>50</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F91" s="3"/>
       <c r="G91" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>345</v>
+        <v>142</v>
       </c>
       <c r="J91" s="3">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>346</v>
+        <v>313</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>253</v>
+        <v>156</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F92" s="3"/>
       <c r="G92" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>299</v>
+        <v>70</v>
       </c>
       <c r="J92" s="3">
-        <v>23</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>166</v>
+        <v>345</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>49</v>
+        <v>123</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F93" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="F93" s="3" t="s">
+        <v>346</v>
+      </c>
       <c r="G93" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>186</v>
+        <v>70</v>
       </c>
       <c r="J93" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>351</v>
+        <v>234</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>172</v>
+        <v>348</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>155</v>
+        <v>223</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F94" s="3"/>
       <c r="G94" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="J94" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>354</v>
+        <v>139</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>355</v>
+        <v>156</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>151</v>
+        <v>50</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F95" s="3"/>
       <c r="G95" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>87</v>
+        <v>241</v>
       </c>
       <c r="J95" s="3">
         <v>3</v>
@@ -4995,38 +5060,306 @@
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F96" s="3"/>
+      <c r="G96" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="J96" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F97" s="3"/>
+      <c r="G97" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H97" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="I97" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="J97" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="B96" s="3" t="s">
+      <c r="B98" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="C96" s="3" t="s">
+      <c r="C98" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F98" s="3"/>
+      <c r="G98" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H98" s="3" t="s">
         <v>359</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="E96" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F96" s="3" t="s">
+      <c r="I98" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="J98" s="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="G96" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H96" s="3" t="s">
+      <c r="B99" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="I96" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="J96" s="3">
-        <v>3</v>
+      <c r="C99" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F99" s="3"/>
+      <c r="G99" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H99" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="I99" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="J99" s="3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F100" s="3"/>
+      <c r="G100" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="J100" s="3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F101" s="3"/>
+      <c r="G101" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="J101" s="3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F102" s="3"/>
+      <c r="G102" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="J102" s="3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E103" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F103" s="3"/>
+      <c r="G103" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H103" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="I103" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="J103" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E104" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F104" s="3"/>
+      <c r="G104" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H104" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="I104" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="J104" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="D105" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="E105" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F105" s="3"/>
+      <c r="G105" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H105" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="I105" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="J105" s="3">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J96"/>
+  <autoFilter ref="A1:J105"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5123,6 +5456,15 @@
     <hyperlink ref="H94" r:id="rId93"/>
     <hyperlink ref="H95" r:id="rId94"/>
     <hyperlink ref="H96" r:id="rId95"/>
+    <hyperlink ref="H97" r:id="rId96"/>
+    <hyperlink ref="H98" r:id="rId97"/>
+    <hyperlink ref="H99" r:id="rId98"/>
+    <hyperlink ref="H100" r:id="rId99"/>
+    <hyperlink ref="H101" r:id="rId100"/>
+    <hyperlink ref="H102" r:id="rId101"/>
+    <hyperlink ref="H103" r:id="rId102"/>
+    <hyperlink ref="H104" r:id="rId103"/>
+    <hyperlink ref="H105" r:id="rId104"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5130,9 +5472,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="40" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="42" customWidth="1"/>
+    <col min="1" max="1" width="44" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="44" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
@@ -5141,162 +5483,295 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>184</v>
+        <v>139</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>185</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>190</v>
+        <v>48</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>191</v>
+        <v>145</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>204</v>
+        <v>169</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>205</v>
+        <v>170</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>194</v>
+        <v>137</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>206</v>
+        <v>172</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>275</v>
+        <v>48</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>241</v>
+        <v>173</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>276</v>
+        <v>174</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>280</v>
+        <v>93</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>281</v>
+        <v>196</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>136</v>
+        <v>197</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>282</v>
+        <v>198</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>231</v>
+        <v>93</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>329</v>
+        <v>227</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>136</v>
+        <v>228</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>330</v>
+        <v>230</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>349</v>
+        <v>231</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>166</v>
+        <v>232</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>194</v>
+        <v>137</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>350</v>
+        <v>233</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>341</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G8"/>
+  <autoFilter ref="A1:G15"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -5305,6 +5780,13 @@
     <hyperlink ref="G6" r:id="rId5"/>
     <hyperlink ref="G7" r:id="rId6"/>
     <hyperlink ref="G8" r:id="rId7"/>
+    <hyperlink ref="G9" r:id="rId8"/>
+    <hyperlink ref="G10" r:id="rId9"/>
+    <hyperlink ref="G11" r:id="rId10"/>
+    <hyperlink ref="G12" r:id="rId11"/>
+    <hyperlink ref="G13" r:id="rId12"/>
+    <hyperlink ref="G14" r:id="rId13"/>
+    <hyperlink ref="G15" r:id="rId14"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5318,15 +5800,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>362</v>
+        <v>382</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>364</v>
+        <v>384</v>
       </c>
       <c r="B2" s="3">
         <v>16</v>
@@ -5334,7 +5816,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>365</v>
+        <v>385</v>
       </c>
       <c r="B3" s="3">
         <v>15</v>
@@ -5342,7 +5824,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>309</v>
+        <v>329</v>
       </c>
       <c r="B4" s="3">
         <v>15</v>
@@ -5350,7 +5832,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>254</v>
+        <v>215</v>
       </c>
       <c r="B5" s="3">
         <v>15</v>
@@ -5358,7 +5840,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B6" s="3">
         <v>10</v>
@@ -5366,7 +5848,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>366</v>
+        <v>386</v>
       </c>
       <c r="B7" s="3">
         <v>9</v>
@@ -5374,7 +5856,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>322</v>
+        <v>346</v>
       </c>
       <c r="B8" s="3">
         <v>9</v>
@@ -5382,7 +5864,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>367</v>
+        <v>387</v>
       </c>
       <c r="B9" s="3">
         <v>9</v>
@@ -5390,7 +5872,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>368</v>
+        <v>388</v>
       </c>
       <c r="B10" s="3">
         <v>8</v>
@@ -5398,15 +5880,15 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>360</v>
+        <v>389</v>
       </c>
       <c r="B11" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>369</v>
+        <v>390</v>
       </c>
       <c r="B12" s="3">
         <v>7</v>
@@ -5414,7 +5896,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>370</v>
+        <v>391</v>
       </c>
       <c r="B13" s="3">
         <v>7</v>
@@ -5422,7 +5904,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>371</v>
+        <v>392</v>
       </c>
       <c r="B14" s="3">
         <v>7</v>
@@ -5430,7 +5912,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>372</v>
+        <v>393</v>
       </c>
       <c r="B15" s="3">
         <v>6</v>
@@ -5438,7 +5920,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>373</v>
+        <v>394</v>
       </c>
       <c r="B16" s="3">
         <v>5</v>
@@ -5457,15 +5939,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>374</v>
+        <v>395</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B2" s="3">
         <v>4</v>
@@ -5473,7 +5955,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B3" s="3">
         <v>3</v>
@@ -5481,7 +5963,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B4" s="3">
         <v>3</v>
@@ -5489,7 +5971,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>166</v>
+        <v>188</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -5497,7 +5979,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>174</v>
+        <v>222</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -5505,15 +5987,15 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>48</v>
+        <v>227</v>
       </c>
       <c r="B7" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>93</v>
+        <v>49</v>
       </c>
       <c r="B8" s="3">
         <v>2</v>
@@ -5521,7 +6003,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
@@ -5529,7 +6011,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -5537,7 +6019,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>142</v>
+        <v>112</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5545,7 +6027,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>170</v>
+        <v>139</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5553,7 +6035,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>172</v>
+        <v>147</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5561,7 +6043,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -5569,7 +6051,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>241</v>
+        <v>173</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -5577,7 +6059,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>273</v>
+        <v>181</v>
       </c>
       <c r="B16" s="3">
         <v>2</v>
@@ -5598,16 +6080,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>375</v>
+        <v>396</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>376</v>
+        <v>397</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>374</v>
+        <v>395</v>
       </c>
     </row>
     <row r="2">
@@ -5615,7 +6097,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C2" s="3">
         <v>13.4</v>
@@ -5629,7 +6111,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C3" s="3">
         <v>12.0</v>
@@ -5643,7 +6125,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C4" s="3">
         <v>7.1</v>
@@ -5657,7 +6139,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C5" s="3">
         <v>7.0</v>
@@ -5671,7 +6153,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C6" s="3">
         <v>6.2</v>
@@ -5685,7 +6167,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C7" s="3">
         <v>6.0</v>
@@ -5699,7 +6181,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>174</v>
+        <v>222</v>
       </c>
       <c r="C8" s="3">
         <v>4.2</v>
@@ -5713,13 +6195,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>111</v>
+        <v>188</v>
       </c>
       <c r="C9" s="3">
-        <v>3.6</v>
+        <v>4.0</v>
       </c>
       <c r="D9" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -5727,13 +6209,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>166</v>
+        <v>112</v>
       </c>
       <c r="C10" s="3">
         <v>3.6</v>
       </c>
       <c r="D10" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -5741,13 +6223,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>56</v>
+        <v>227</v>
       </c>
       <c r="C11" s="3">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="D11" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -5755,13 +6237,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>172</v>
+        <v>57</v>
       </c>
       <c r="C12" s="3">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="D12" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -5769,7 +6251,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>281</v>
+        <v>139</v>
       </c>
       <c r="C13" s="3">
         <v>2.8</v>
@@ -5783,13 +6265,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>126</v>
+        <v>167</v>
       </c>
       <c r="C14" s="3">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="D14" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -5797,10 +6279,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>142</v>
+        <v>173</v>
       </c>
       <c r="C15" s="3">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="D15" s="3">
         <v>2</v>
@@ -5811,10 +6293,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>170</v>
+        <v>300</v>
       </c>
       <c r="C16" s="3">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="D16" s="3">
         <v>2</v>
@@ -5834,46 +6316,46 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>377</v>
+        <v>398</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>378</v>
+        <v>399</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>379</v>
+        <v>171</v>
       </c>
       <c r="B2" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>380</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B3" s="3">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>381</v>
+        <v>400</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B4" s="3">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>382</v>
+        <v>401</v>
       </c>
     </row>
   </sheetData>
@@ -5889,39 +6371,39 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>377</v>
+        <v>398</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B2" s="3">
-        <v>67</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B3" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B4" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -5929,7 +6411,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B6" s="3">
         <v>2</v>
@@ -5937,15 +6419,15 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B7" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B8" s="3">
         <v>1</v>
@@ -5953,7 +6435,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="B9" s="3">
         <v>1</v>
@@ -5980,34 +6462,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>375</v>
+        <v>396</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>383</v>
+        <v>402</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>384</v>
+        <v>403</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>385</v>
+        <v>404</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2">
@@ -6015,31 +6497,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>386</v>
+        <v>405</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>387</v>
+        <v>406</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>388</v>
+        <v>407</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>389</v>
+        <v>408</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="3">
@@ -6047,31 +6529,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>390</v>
+        <v>409</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>391</v>
+        <v>410</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>392</v>
+        <v>411</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>393</v>
+        <v>412</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>394</v>
+        <v>413</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>395</v>
+        <v>414</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>396</v>
+        <v>415</v>
       </c>
     </row>
     <row r="4">
@@ -6079,31 +6561,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>397</v>
+        <v>416</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>398</v>
+        <v>417</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>136</v>
+        <v>223</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>393</v>
+        <v>418</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>399</v>
+        <v>419</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>73</v>
+        <v>186</v>
       </c>
     </row>
     <row r="5">
@@ -6111,31 +6593,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>401</v>
+        <v>421</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>402</v>
+        <v>332</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>403</v>
+        <v>140</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>393</v>
+        <v>412</v>
       </c>
       <c r="F5" s="3">
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>404</v>
+        <v>422</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>405</v>
+        <v>423</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>147</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6">
@@ -6143,31 +6625,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>406</v>
+        <v>424</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>407</v>
+        <v>425</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>408</v>
+        <v>426</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="F6" s="3">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>410</v>
+        <v>427</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>411</v>
+        <v>428</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>412</v>
+        <v>219</v>
       </c>
     </row>
     <row r="7">
@@ -6175,31 +6657,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>413</v>
+        <v>429</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>212</v>
+        <v>431</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>393</v>
+        <v>432</v>
       </c>
       <c r="F7" s="3">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>415</v>
+        <v>433</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>203</v>
+        <v>435</v>
       </c>
     </row>
     <row r="8">
@@ -6207,31 +6689,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>417</v>
+        <v>436</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>174</v>
+        <v>437</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>175</v>
+        <v>228</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>393</v>
+        <v>412</v>
       </c>
       <c r="F8" s="3">
         <v>84</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>418</v>
+        <v>438</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>419</v>
+        <v>439</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>420</v>
+        <v>206</v>
       </c>
     </row>
     <row r="9">
@@ -6239,31 +6721,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>421</v>
+        <v>440</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>422</v>
+        <v>222</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>194</v>
+        <v>254</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="F9" s="3">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>424</v>
+        <v>441</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>425</v>
+        <v>442</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>426</v>
+        <v>443</v>
       </c>
     </row>
     <row r="10">
@@ -6271,31 +6753,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>427</v>
+        <v>444</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>428</v>
+        <v>445</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>393</v>
+        <v>446</v>
       </c>
       <c r="F10" s="3">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>429</v>
+        <v>447</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>431</v>
+        <v>334</v>
       </c>
     </row>
     <row r="11">
@@ -6303,31 +6785,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>432</v>
+        <v>449</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>433</v>
+        <v>450</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>434</v>
+        <v>140</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>387</v>
+        <v>412</v>
       </c>
       <c r="F11" s="3">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>435</v>
+        <v>451</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>436</v>
+        <v>452</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>46</v>
+        <v>453</v>
       </c>
     </row>
     <row r="12">
@@ -6335,31 +6817,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>437</v>
+        <v>454</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>422</v>
+        <v>445</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>194</v>
+        <v>144</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>423</v>
+        <v>446</v>
       </c>
       <c r="F12" s="3">
         <v>74</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>438</v>
+        <v>455</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>439</v>
+        <v>456</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>420</v>
+        <v>443</v>
       </c>
     </row>
     <row r="13">
@@ -6367,31 +6849,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>440</v>
+        <v>457</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>441</v>
+        <v>458</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>442</v>
+        <v>459</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>423</v>
+        <v>446</v>
       </c>
       <c r="F13" s="3">
         <v>70</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>443</v>
+        <v>460</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>444</v>
+        <v>461</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14">
@@ -6399,31 +6881,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>445</v>
+        <v>462</v>
       </c>
       <c r="C14" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>446</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>423</v>
       </c>
       <c r="F14" s="3">
         <v>70</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>447</v>
+        <v>464</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>448</v>
+        <v>465</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="15">
@@ -6431,31 +6913,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>449</v>
+        <v>466</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>450</v>
+        <v>467</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>451</v>
+        <v>468</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>393</v>
+        <v>412</v>
       </c>
       <c r="F15" s="3">
         <v>68</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>452</v>
+        <v>469</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>453</v>
+        <v>470</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>454</v>
+        <v>471</v>
       </c>
     </row>
     <row r="16">
@@ -6463,31 +6945,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>455</v>
+        <v>472</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>456</v>
+        <v>473</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>387</v>
+        <v>406</v>
       </c>
       <c r="F16" s="3">
         <v>61</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>457</v>
+        <v>474</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>458</v>
+        <v>475</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -6495,31 +6977,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>459</v>
+        <v>476</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>460</v>
+        <v>477</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>355</v>
+        <v>380</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>409</v>
+        <v>432</v>
       </c>
       <c r="F17" s="3">
         <v>57</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>461</v>
+        <v>478</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>462</v>
+        <v>479</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>168</v>
+        <v>241</v>
       </c>
     </row>
     <row r="18">
@@ -6527,31 +7009,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>463</v>
+        <v>480</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>464</v>
+        <v>481</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>393</v>
+        <v>412</v>
       </c>
       <c r="F18" s="3">
         <v>52</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>465</v>
+        <v>482</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>466</v>
+        <v>483</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="19">
@@ -6559,31 +7041,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>467</v>
+        <v>484</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>468</v>
+        <v>485</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>469</v>
+        <v>486</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>393</v>
+        <v>412</v>
       </c>
       <c r="F19" s="3">
         <v>48</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>470</v>
+        <v>487</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>471</v>
+        <v>488</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>177</v>
+        <v>489</v>
       </c>
     </row>
     <row r="20">
@@ -6591,31 +7073,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>472</v>
+        <v>490</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>473</v>
+        <v>491</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>409</v>
+        <v>432</v>
       </c>
       <c r="F20" s="3">
         <v>46</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>474</v>
+        <v>492</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>475</v>
+        <v>493</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="21">
@@ -6623,31 +7105,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>476</v>
+        <v>494</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>305</v>
+        <v>325</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>393</v>
+        <v>412</v>
       </c>
       <c r="F21" s="3">
         <v>44</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>477</v>
+        <v>495</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>478</v>
+        <v>496</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
